--- a/IQ-guide.xlsx
+++ b/IQ-guide.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="خطة المذاكرة" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'أسئلة IQ'!$A$1:$H$89</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'أسئلة IQ'!$A$1:$H$179</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="20">
+  <fonts count="27">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -103,6 +103,48 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="0090be6d"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00118ab2"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="002d6a4f"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00bc6c25"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="000b7285"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00d6336c"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="005a189a"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00e76f51"/>
       <sz val="11"/>
     </font>
     <font>
@@ -201,7 +243,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -242,32 +284,53 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="25" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1980,7 +2043,7 @@
       <row>66</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="3048000" cy="1028700"/>
+    <ext cx="3048000" cy="1190625"/>
     <pic>
       <nvPicPr>
         <cNvPr id="66" name="Image 66" descr="Picture"/>
@@ -2538,6 +2601,2256 @@
       </nvPicPr>
       <blipFill>
         <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId88"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>89</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2838450" cy="1809750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="89" name="Image 89" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId89"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>90</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3048000" cy="1123950"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="90" name="Image 90" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId90"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>91</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2838450" cy="1809750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="91" name="Image 91" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId91"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>92</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2838450" cy="1809750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="92" name="Image 92" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId92"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>93</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2838450" cy="1809750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="93" name="Image 93" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId93"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>94</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2838450" cy="1809750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="94" name="Image 94" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId94"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>95</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2838450" cy="1809750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="95" name="Image 95" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId95"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>96</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2838450" cy="1809750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="96" name="Image 96" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId96"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>97</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3048000" cy="1123950"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="97" name="Image 97" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId97"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>98</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2838450" cy="1809750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="98" name="Image 98" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId98"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>99</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2838450" cy="1809750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="99" name="Image 99" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId99"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>100</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2838450" cy="1809750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="100" name="Image 100" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId100"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>101</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2838450" cy="1809750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="101" name="Image 101" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId101"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>102</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2838450" cy="1809750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="102" name="Image 102" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId102"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>103</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2838450" cy="1809750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="103" name="Image 103" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId103"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>104</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2838450" cy="1809750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="104" name="Image 104" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId104"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>105</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2838450" cy="1809750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="105" name="Image 105" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId105"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>106</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2838450" cy="1809750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="106" name="Image 106" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId106"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>107</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2838450" cy="1809750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="107" name="Image 107" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId107"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>108</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2838450" cy="1809750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="108" name="Image 108" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId108"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>109</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2838450" cy="1809750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="109" name="Image 109" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId109"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>110</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2838450" cy="1809750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="110" name="Image 110" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId110"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>111</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2838450" cy="1809750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="111" name="Image 111" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId111"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>112</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2838450" cy="1809750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="112" name="Image 112" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId112"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>113</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2838450" cy="1809750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="113" name="Image 113" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId113"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>114</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2838450" cy="1809750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="114" name="Image 114" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId114"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>115</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2838450" cy="1809750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="115" name="Image 115" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId115"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>116</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3048000" cy="1123950"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="116" name="Image 116" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId116"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>117</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2838450" cy="1809750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="117" name="Image 117" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId117"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>118</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2838450" cy="1809750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="118" name="Image 118" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId118"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>119</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3048000" cy="1123950"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="119" name="Image 119" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId119"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>120</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2838450" cy="1809750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="120" name="Image 120" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId120"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>121</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2838450" cy="1809750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="121" name="Image 121" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId121"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>122</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2838450" cy="1809750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="122" name="Image 122" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId122"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>123</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2838450" cy="1809750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="123" name="Image 123" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId123"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>124</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2838450" cy="1809750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="124" name="Image 124" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId124"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>125</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2838450" cy="1809750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="125" name="Image 125" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId125"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>126</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3048000" cy="1714500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="126" name="Image 126" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId126"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>127</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3048000" cy="1714500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="127" name="Image 127" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId127"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>128</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3048000" cy="1714500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="128" name="Image 128" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId128"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>129</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3048000" cy="1714500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="129" name="Image 129" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId129"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>130</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3048000" cy="1714500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="130" name="Image 130" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId130"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>131</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3048000" cy="1714500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="131" name="Image 131" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId131"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>132</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3048000" cy="1714500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="132" name="Image 132" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId132"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>133</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3048000" cy="1714500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="133" name="Image 133" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId133"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>134</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3048000" cy="1714500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="134" name="Image 134" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId134"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>135</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3048000" cy="1714500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="135" name="Image 135" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId135"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>136</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3048000" cy="1714500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="136" name="Image 136" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId136"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>137</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3048000" cy="1714500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="137" name="Image 137" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId137"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>138</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3048000" cy="1714500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="138" name="Image 138" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId138"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>139</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3048000" cy="1714500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="139" name="Image 139" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId139"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>140</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3048000" cy="1714500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="140" name="Image 140" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId140"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>141</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3048000" cy="1714500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="141" name="Image 141" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId141"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>142</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3048000" cy="1714500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="142" name="Image 142" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId142"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>143</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3048000" cy="1714500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="143" name="Image 143" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId143"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>144</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3048000" cy="1714500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="144" name="Image 144" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId144"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>145</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3048000" cy="1714500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="145" name="Image 145" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId145"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>146</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3048000" cy="1714500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="146" name="Image 146" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId146"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>147</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3048000" cy="1714500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="147" name="Image 147" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId147"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>148</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3048000" cy="1714500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="148" name="Image 148" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId148"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>149</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3048000" cy="1524000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="149" name="Image 149" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId149"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>150</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3048000" cy="1524000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="150" name="Image 150" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId150"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>151</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3048000" cy="1524000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="151" name="Image 151" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId151"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>152</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3048000" cy="1524000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="152" name="Image 152" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId152"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>153</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3048000" cy="1524000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="153" name="Image 153" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId153"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>154</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3048000" cy="1524000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="154" name="Image 154" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId154"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>155</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3048000" cy="400050"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="155" name="Image 155" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId155"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>156</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3048000" cy="533400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="156" name="Image 156" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId156"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>157</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3048000" cy="533400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="157" name="Image 157" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId157"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>158</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3048000" cy="638175"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="158" name="Image 158" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId158"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>159</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3048000" cy="533400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="159" name="Image 159" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId159"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>160</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3048000" cy="638175"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="160" name="Image 160" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId160"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>161</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3048000" cy="638175"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="161" name="Image 161" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId161"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>162</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3048000" cy="638175"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="162" name="Image 162" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId162"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>163</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3048000" cy="638175"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="163" name="Image 163" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId163"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>164</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3048000" cy="533400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="164" name="Image 164" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId164"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>165</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3048000" cy="638175"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="165" name="Image 165" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId165"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>166</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3048000" cy="800100"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="166" name="Image 166" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId166"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>167</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2600325" cy="1809750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="167" name="Image 167" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId167"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>168</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2600325" cy="1809750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="168" name="Image 168" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId168"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>169</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2600325" cy="1809750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="169" name="Image 169" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId169"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>170</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3048000" cy="781050"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="170" name="Image 170" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId170"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>171</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3048000" cy="781050"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="171" name="Image 171" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId171"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>172</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3048000" cy="733425"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="172" name="Image 172" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId172"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>173</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3048000" cy="781050"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="173" name="Image 173" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId173"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>174</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3048000" cy="733425"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="174" name="Image 174" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId174"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>175</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3048000" cy="781050"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="175" name="Image 175" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId175"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>176</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2895600" cy="1809750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="176" name="Image 176" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId176"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>177</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2152650" cy="1809750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="177" name="Image 177" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId177"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>178</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2152650" cy="1809750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="178" name="Image 178" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId178"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -2840,7 +5153,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H89"/>
+  <dimension ref="A1:H179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5984,8 +8297,3017 @@
         </is>
       </c>
     </row>
+    <row r="90" ht="156.2" customHeight="1">
+      <c r="A90" s="14" t="inlineStr">
+        <is>
+          <t>💭 التفكير المجرد — العلاقة بين الأشياء</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C90" s="4" t="inlineStr">
+        <is>
+          <t>القلم ↔ الفرشاة</t>
+        </is>
+      </c>
+      <c r="E90" s="5" t="inlineStr">
+        <is>
+          <t>ما العلاقة أو أوجه الشبه بين «القلم» و«الفرشاة»؟</t>
+        </is>
+      </c>
+      <c r="F90" s="5" t="inlineStr">
+        <is>
+          <t>1. اسأل: ما الذي يفعله كل منهما؟ كلاهما يترك أثرًا على سطح للتعبير عن فكرة.
+2. كلاهما أداة يدوية للرسم/الكتابة، فالعلاقة هي «وظيفة متشابهة».
+3. إن وُجد اختيار «أدوات للتعبير» مع «للكتابة أو الرسم» فالأول أعمّ وأدق.</t>
+        </is>
+      </c>
+      <c r="G90" s="6" t="inlineStr">
+        <is>
+          <t>✔ كلاهما يستخدم للكتابة أو الرسم — أو «أدوات للتعبير» حسب الاختيارات</t>
+        </is>
+      </c>
+      <c r="H90" s="5" t="inlineStr"/>
+    </row>
+    <row r="91" ht="100.04" customHeight="1">
+      <c r="A91" s="14" t="inlineStr">
+        <is>
+          <t>💭 التفكير المجرد — العلاقة بين الأشياء</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C91" s="4" t="inlineStr">
+        <is>
+          <t>الشوكة ↔ الملعقة</t>
+        </is>
+      </c>
+      <c r="E91" s="5" t="inlineStr">
+        <is>
+          <t>ما العلاقة أو أوجه الشبه بين «الشوكة» و«الملعقة»؟</t>
+        </is>
+      </c>
+      <c r="F91" s="5" t="inlineStr">
+        <is>
+          <t>1. الجواب السهل: كلاهما من أدوات المائدة لتناول الطعام.
+2. لكن الأدق: كلاهما من نفس المادة؛ لأن ناسًا كثيرين لا يأكلون بالشوكة أو الملعقة.
+3. قاعدة: الإجابة التي تصدق على الجميع بلا استثناء هي الأدق.</t>
+        </is>
+      </c>
+      <c r="G91" s="6" t="inlineStr">
+        <is>
+          <t>✔ الأدق: كلاهما مصنوع من نفس المادة (معدن أو بلاستيك) — و«أدوات مائدة» صحيح أيضًا</t>
+        </is>
+      </c>
+      <c r="H91" s="5" t="inlineStr"/>
+    </row>
+    <row r="92" ht="156.2" customHeight="1">
+      <c r="A92" s="14" t="inlineStr">
+        <is>
+          <t>💭 التفكير المجرد — العلاقة بين الأشياء</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C92" s="4" t="inlineStr">
+        <is>
+          <t>الساعة ↔ البوصلة</t>
+        </is>
+      </c>
+      <c r="E92" s="5" t="inlineStr">
+        <is>
+          <t>ما العلاقة أو أوجه الشبه بين «الساعة» و«البوصلة»؟</t>
+        </is>
+      </c>
+      <c r="F92" s="5" t="inlineStr">
+        <is>
+          <t>1. ابدأ بالفرق: الوظيفة مختلفة تمامًا (زمن مقابل اتجاه).
+2. ثم ابحث عن الجامع: كلاهما أداة دقيقة يستخدمها الإنسان لتنظيم حياته أو رحلته.
+3. «أدوات للملاحة والتنظيم» يجمع الاثنين معًا.</t>
+        </is>
+      </c>
+      <c r="G92" s="6" t="inlineStr">
+        <is>
+          <t>✔ الفرق: الساعة لقياس الوقت والبوصلة لتحديد الاتجاه — والجامع: كلاهما أدوات للملاحة والتنظيم</t>
+        </is>
+      </c>
+      <c r="H92" s="5" t="inlineStr"/>
+    </row>
+    <row r="93" ht="156.2" customHeight="1">
+      <c r="A93" s="14" t="inlineStr">
+        <is>
+          <t>💭 التفكير المجرد — العلاقة بين الأشياء</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C93" s="4" t="inlineStr">
+        <is>
+          <t>العين ↔ الكاميرا</t>
+        </is>
+      </c>
+      <c r="E93" s="5" t="inlineStr">
+        <is>
+          <t>ما العلاقة أو أوجه الشبه بين «العين» و«الكاميرا»؟</t>
+        </is>
+      </c>
+      <c r="F93" s="5" t="inlineStr">
+        <is>
+          <t>1. العلاقة هنا «طبيعي ↔ صناعي يؤدي نفس الوظيفة».
+2. العين تبصر والكاميرا تلتقط — والجامع تكوين صورة.
+3. استبعد «كلاهما زجاج/إلكتروني» لأنها لا تصدق على العين.</t>
+        </is>
+      </c>
+      <c r="G93" s="6" t="inlineStr">
+        <is>
+          <t>✔ كلاهما يستخدم للرؤية أو الالتقاط (العضو الطبيعي ونظيره الصناعي)</t>
+        </is>
+      </c>
+      <c r="H93" s="5" t="inlineStr"/>
+    </row>
+    <row r="94" ht="156.2" customHeight="1">
+      <c r="A94" s="14" t="inlineStr">
+        <is>
+          <t>💭 التفكير المجرد — العلاقة بين الأشياء</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C94" s="4" t="inlineStr">
+        <is>
+          <t>الهاتف ↔ التلفاز</t>
+        </is>
+      </c>
+      <c r="E94" s="5" t="inlineStr">
+        <is>
+          <t>ما العلاقة أو أوجه الشبه بين «الهاتف» و«التلفاز»؟</t>
+        </is>
+      </c>
+      <c r="F94" s="5" t="inlineStr">
+        <is>
+          <t>1. كلاهما شاشة تعرض محتوى مرئيًا ومسموعًا.
+2. الجامع الأقوى: نقل الصوت والصورة؛ ثم «وسائل تواصل» أو «ترفيه» حسب الخيارات.
+3. «أجهزة كهربائية» صحيح لكنه سطحي — لا تختره إن وُجد ما هو أدق.</t>
+        </is>
+      </c>
+      <c r="G94" s="6" t="inlineStr">
+        <is>
+          <t>✔ كلاهما وسيلة ترفيه أو تواصل، وكلاهما ينقل صوتًا وصورة (حسب الاختيارات)</t>
+        </is>
+      </c>
+      <c r="H94" s="5" t="inlineStr"/>
+    </row>
+    <row r="95" ht="156.2" customHeight="1">
+      <c r="A95" s="14" t="inlineStr">
+        <is>
+          <t>💭 التفكير المجرد — العلاقة بين الأشياء</t>
+        </is>
+      </c>
+      <c r="B95" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C95" s="4" t="inlineStr">
+        <is>
+          <t>الحجر ↔ الورقة</t>
+        </is>
+      </c>
+      <c r="E95" s="5" t="inlineStr">
+        <is>
+          <t>ما العلاقة أو أوجه الشبه بين «الحجر» و«الورقة»؟</t>
+        </is>
+      </c>
+      <c r="F95" s="5" t="inlineStr">
+        <is>
+          <t>1. هذا النوع اسمه «كيف يمكن استخدامهما بطريقة غير تقليدية؟».
+2. تخيّل موقفًا واحدًا يجمع الاثنين في وظيفة جديدة.
+3. أي إجابة تربطهما بفعل واحد مقبولة — رجّح ما يناسب الاختيارات.</t>
+        </is>
+      </c>
+      <c r="G95" s="6" t="inlineStr">
+        <is>
+          <t>✔ استخدام غير تقليدي: الورقة خريطة والحجر لتحديد المكان — أو الورقة مظلة صغيرة والحجر لتثبيتها</t>
+        </is>
+      </c>
+      <c r="H95" s="5" t="inlineStr">
+        <is>
+          <t>أسئلة التفكير الإبداعي ليس لها خطأ واحد واضح: بل أقرب إجابة.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="156.2" customHeight="1">
+      <c r="A96" s="14" t="inlineStr">
+        <is>
+          <t>💭 التفكير المجرد — العلاقة بين الأشياء</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C96" s="4" t="inlineStr">
+        <is>
+          <t>الطائرة ↔ الطير</t>
+        </is>
+      </c>
+      <c r="E96" s="5" t="inlineStr">
+        <is>
+          <t>ما العلاقة أو أوجه الشبه بين «الطائرة» و«الطير»؟</t>
+        </is>
+      </c>
+      <c r="F96" s="5" t="inlineStr">
+        <is>
+          <t>1. الطائرة محاكاة صناعية للطير في الطيران.
+2. الجامع: الطيران + الأجنحة + الاعتماد على الهواء.
+3. إن وُجد «كل ذلك» فهو الاختيار الجامع.</t>
+        </is>
+      </c>
+      <c r="G96" s="6" t="inlineStr">
+        <is>
+          <t>✔ كلاهما يطير ولهما أجنحة ويستخدمان الهواء للتحليق</t>
+        </is>
+      </c>
+      <c r="H96" s="5" t="inlineStr"/>
+    </row>
+    <row r="97" ht="156.2" customHeight="1">
+      <c r="A97" s="14" t="inlineStr">
+        <is>
+          <t>💭 التفكير المجرد — العلاقة بين الأشياء</t>
+        </is>
+      </c>
+      <c r="B97" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C97" s="4" t="inlineStr">
+        <is>
+          <t>الكتاب ↔ الحاسوب</t>
+        </is>
+      </c>
+      <c r="E97" s="5" t="inlineStr">
+        <is>
+          <t>ما العلاقة أو أوجه الشبه بين «الكتاب» و«الحاسوب»؟</t>
+        </is>
+      </c>
+      <c r="F97" s="5" t="inlineStr">
+        <is>
+          <t>1. كلاهما وعاء للمعرفة.
+2. القديم والحديث لنفس الوظيفة: حفظ المعلومات واسترجاعها.
+3. استبعد «إلكتروني/ورقي» لأنها تصدق على واحد فقط.</t>
+        </is>
+      </c>
+      <c r="G97" s="6" t="inlineStr">
+        <is>
+          <t>✔ كلاهما يستخدم للبحث عن المعلومات والتعلم</t>
+        </is>
+      </c>
+      <c r="H97" s="5" t="inlineStr"/>
+    </row>
+    <row r="98" ht="100.04" customHeight="1">
+      <c r="A98" s="14" t="inlineStr">
+        <is>
+          <t>💭 التفكير المجرد — العلاقة بين الأشياء</t>
+        </is>
+      </c>
+      <c r="B98" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="C98" s="4" t="inlineStr">
+        <is>
+          <t>الشمس ↔ المصباح</t>
+        </is>
+      </c>
+      <c r="E98" s="5" t="inlineStr">
+        <is>
+          <t>ما العلاقة أو أوجه الشبه بين «الشمس» و«المصباح»؟</t>
+        </is>
+      </c>
+      <c r="F98" s="5" t="inlineStr">
+        <is>
+          <t>1. الشمس مصدر طبيعي والمصباح مصدر صناعي.
+2. الجامع: إصدار الضوء.
+3. «الحرارة» تصدق على الشمس أكثر فلا تخترها.</t>
+        </is>
+      </c>
+      <c r="G98" s="6" t="inlineStr">
+        <is>
+          <t>✔ كلاهما مصدر للضوء</t>
+        </is>
+      </c>
+      <c r="H98" s="5" t="inlineStr"/>
+    </row>
+    <row r="99" ht="156.2" customHeight="1">
+      <c r="A99" s="14" t="inlineStr">
+        <is>
+          <t>💭 التفكير المجرد — العلاقة بين الأشياء</t>
+        </is>
+      </c>
+      <c r="B99" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C99" s="4" t="inlineStr">
+        <is>
+          <t>السمكة ↔ الغواصة</t>
+        </is>
+      </c>
+      <c r="E99" s="5" t="inlineStr">
+        <is>
+          <t>ما العلاقة أو أوجه الشبه بين «السمكة» و«الغواصة»؟</t>
+        </is>
+      </c>
+      <c r="F99" s="5" t="inlineStr">
+        <is>
+          <t>1. الغواصة محاكاة صناعية للسمكة في بيئتها.
+2. الجامع: الحركة داخل الماء.
+3. «معدني/للنقل» لا يصدق على السمكة.</t>
+        </is>
+      </c>
+      <c r="G99" s="6" t="inlineStr">
+        <is>
+          <t>✔ كلاهما يتحرك داخل الماء</t>
+        </is>
+      </c>
+      <c r="H99" s="5" t="inlineStr"/>
+    </row>
+    <row r="100" ht="156.2" customHeight="1">
+      <c r="A100" s="14" t="inlineStr">
+        <is>
+          <t>💭 التفكير المجرد — العلاقة بين الأشياء</t>
+        </is>
+      </c>
+      <c r="B100" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="C100" s="4" t="inlineStr">
+        <is>
+          <t>النظارة ↔ العدسة المكبرة</t>
+        </is>
+      </c>
+      <c r="E100" s="5" t="inlineStr">
+        <is>
+          <t>ما العلاقة أو أوجه الشبه بين «النظارة» و«العدسة المكبرة»؟</t>
+        </is>
+      </c>
+      <c r="F100" s="5" t="inlineStr">
+        <is>
+          <t>1. كلاهما عدسة تعالج ضعف الرؤية أو تضخّم الصورة.
+2. الجامع: تحسين الرؤية لا مجرد «الزجاج».</t>
+        </is>
+      </c>
+      <c r="G100" s="6" t="inlineStr">
+        <is>
+          <t>✔ كلاهما يستخدم لتحسين الرؤية</t>
+        </is>
+      </c>
+      <c r="H100" s="5" t="inlineStr"/>
+    </row>
+    <row r="101" ht="156.2" customHeight="1">
+      <c r="A101" s="14" t="inlineStr">
+        <is>
+          <t>💭 التفكير المجرد — العلاقة بين الأشياء</t>
+        </is>
+      </c>
+      <c r="B101" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="C101" s="4" t="inlineStr">
+        <is>
+          <t>الميزان ↔ الحكم</t>
+        </is>
+      </c>
+      <c r="E101" s="5" t="inlineStr">
+        <is>
+          <t>ما العلاقة أو أوجه الشبه بين «الميزان» و«الحكم»؟</t>
+        </is>
+      </c>
+      <c r="F101" s="5" t="inlineStr">
+        <is>
+          <t>1. الميزان أداة حسية والحكم أداة معنوية لنفس الفكرة.
+2. الجامع: التقييم والترجيح.</t>
+        </is>
+      </c>
+      <c r="G101" s="6" t="inlineStr">
+        <is>
+          <t>✔ كلاهما يقيم أو يحدد من الأفضل أو الأصح</t>
+        </is>
+      </c>
+      <c r="H101" s="5" t="inlineStr"/>
+    </row>
+    <row r="102" ht="156.2" customHeight="1">
+      <c r="A102" s="14" t="inlineStr">
+        <is>
+          <t>💭 التفكير المجرد — العلاقة بين الأشياء</t>
+        </is>
+      </c>
+      <c r="B102" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="C102" s="4" t="inlineStr">
+        <is>
+          <t>النافذة ↔ شاشة التلفاز</t>
+        </is>
+      </c>
+      <c r="E102" s="5" t="inlineStr">
+        <is>
+          <t>ما العلاقة أو أوجه الشبه بين «النافذة» و«شاشة التلفاز»؟</t>
+        </is>
+      </c>
+      <c r="F102" s="5" t="inlineStr">
+        <is>
+          <t>1. كلاهما «إطار» ترى من خلاله مشهدًا لست فيه.
+2. الجامع: نقل صورة من مكان إلى آخر.</t>
+        </is>
+      </c>
+      <c r="G102" s="6" t="inlineStr">
+        <is>
+          <t>✔ كلاهما يظهر صورة لما بالخارج أو لمكان آخر</t>
+        </is>
+      </c>
+      <c r="H102" s="5" t="inlineStr"/>
+    </row>
+    <row r="103" ht="156.2" customHeight="1">
+      <c r="A103" s="14" t="inlineStr">
+        <is>
+          <t>💭 التفكير المجرد — العلاقة بين الأشياء</t>
+        </is>
+      </c>
+      <c r="B103" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="C103" s="4" t="inlineStr">
+        <is>
+          <t>السيارة ↔ الدراجة</t>
+        </is>
+      </c>
+      <c r="E103" s="5" t="inlineStr">
+        <is>
+          <t>ما العلاقة أو أوجه الشبه بين «السيارة» و«الدراجة»؟</t>
+        </is>
+      </c>
+      <c r="F103" s="5" t="inlineStr">
+        <is>
+          <t>1. الجامع: التنقل + الاعتماد على العجلات.
+2. «بمحرك» لا يصدق على الدراجة، فاستبعده.</t>
+        </is>
+      </c>
+      <c r="G103" s="6" t="inlineStr">
+        <is>
+          <t>✔ وسيلة نقل تعتمد على العجلات</t>
+        </is>
+      </c>
+      <c r="H103" s="5" t="inlineStr"/>
+    </row>
+    <row r="104" ht="156.2" customHeight="1">
+      <c r="A104" s="14" t="inlineStr">
+        <is>
+          <t>💭 التفكير المجرد — العلاقة بين الأشياء</t>
+        </is>
+      </c>
+      <c r="B104" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="C104" s="4" t="inlineStr">
+        <is>
+          <t>الكتاب ↔ الفيلم الوثائقي</t>
+        </is>
+      </c>
+      <c r="E104" s="5" t="inlineStr">
+        <is>
+          <t>ما العلاقة أو أوجه الشبه بين «الكتاب» و«الفيلم الوثائقي»؟</t>
+        </is>
+      </c>
+      <c r="F104" s="5" t="inlineStr">
+        <is>
+          <t>1. مكتوب مقابل مرئي لنفس الغاية.</t>
+        </is>
+      </c>
+      <c r="G104" s="6" t="inlineStr">
+        <is>
+          <t>✔ كلاهما وسيلة لنقل المعرفة والمعلومات</t>
+        </is>
+      </c>
+      <c r="H104" s="5" t="inlineStr"/>
+    </row>
+    <row r="105" ht="156.2" customHeight="1">
+      <c r="A105" s="14" t="inlineStr">
+        <is>
+          <t>💭 التفكير المجرد — العلاقة بين الأشياء</t>
+        </is>
+      </c>
+      <c r="B105" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C105" s="4" t="inlineStr">
+        <is>
+          <t>الوردة ↔ الإنسان</t>
+        </is>
+      </c>
+      <c r="E105" s="5" t="inlineStr">
+        <is>
+          <t>ما العلاقة أو أوجه الشبه بين «الوردة» و«الإنسان»؟</t>
+        </is>
+      </c>
+      <c r="F105" s="5" t="inlineStr">
+        <is>
+          <t>1. الجامع: كائن حيّ له احتياجات ودورة حياة.
+2. «جميل/طبيعة» انطباع سطحي لا علاقة موضوعية.</t>
+        </is>
+      </c>
+      <c r="G105" s="6" t="inlineStr">
+        <is>
+          <t>✔ كلاهما يحتاج إلى الهواء والماء وله دورة حياة</t>
+        </is>
+      </c>
+      <c r="H105" s="5" t="inlineStr"/>
+    </row>
+    <row r="106" ht="156.2" customHeight="1">
+      <c r="A106" s="14" t="inlineStr">
+        <is>
+          <t>💭 التفكير المجرد — العلاقة بين الأشياء</t>
+        </is>
+      </c>
+      <c r="B106" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="C106" s="4" t="inlineStr">
+        <is>
+          <t>الراديو ↔ الأذن</t>
+        </is>
+      </c>
+      <c r="E106" s="5" t="inlineStr">
+        <is>
+          <t>ما العلاقة أو أوجه الشبه بين «الراديو» و«الأذن»؟</t>
+        </is>
+      </c>
+      <c r="F106" s="5" t="inlineStr">
+        <is>
+          <t>1. الراديو يلتقط الموجات والأذن تلتقط الذبذبات.</t>
+        </is>
+      </c>
+      <c r="G106" s="6" t="inlineStr">
+        <is>
+          <t>✔ كلاهما يلتقط الأصوات</t>
+        </is>
+      </c>
+      <c r="H106" s="5" t="inlineStr"/>
+    </row>
+    <row r="107" ht="156.2" customHeight="1">
+      <c r="A107" s="14" t="inlineStr">
+        <is>
+          <t>💭 التفكير المجرد — العلاقة بين الأشياء</t>
+        </is>
+      </c>
+      <c r="B107" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="C107" s="4" t="inlineStr">
+        <is>
+          <t>المدرسة ↔ البيت</t>
+        </is>
+      </c>
+      <c r="E107" s="5" t="inlineStr">
+        <is>
+          <t>ما العلاقة أو أوجه الشبه بين «المدرسة» و«البيت»؟</t>
+        </is>
+      </c>
+      <c r="F107" s="5" t="inlineStr">
+        <is>
+          <t>1. المعنى الوظيفي لا الشكلي هو المطلوب.</t>
+        </is>
+      </c>
+      <c r="G107" s="6" t="inlineStr">
+        <is>
+          <t>✔ كلاهما مكان للتعلم والتربية</t>
+        </is>
+      </c>
+      <c r="H107" s="5" t="inlineStr"/>
+    </row>
+    <row r="108" ht="156.2" customHeight="1">
+      <c r="A108" s="14" t="inlineStr">
+        <is>
+          <t>💭 التفكير المجرد — العلاقة بين الأشياء</t>
+        </is>
+      </c>
+      <c r="B108" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="C108" s="4" t="inlineStr">
+        <is>
+          <t>الوقت ↔ المال</t>
+        </is>
+      </c>
+      <c r="E108" s="5" t="inlineStr">
+        <is>
+          <t>ما العلاقة أو أوجه الشبه بين «الوقت» و«المال»؟</t>
+        </is>
+      </c>
+      <c r="F108" s="5" t="inlineStr">
+        <is>
+          <t>1. الجامع: مورد قابل للإدارة والحساب.</t>
+        </is>
+      </c>
+      <c r="G108" s="6" t="inlineStr">
+        <is>
+          <t>✔ كلاهما مهم ويمكن إدارته وحسابه</t>
+        </is>
+      </c>
+      <c r="H108" s="5" t="inlineStr"/>
+    </row>
+    <row r="109" ht="156.2" customHeight="1">
+      <c r="A109" s="14" t="inlineStr">
+        <is>
+          <t>💭 التفكير المجرد — العلاقة بين الأشياء</t>
+        </is>
+      </c>
+      <c r="B109" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="C109" s="4" t="inlineStr">
+        <is>
+          <t>الطبيب ↔ الصيدلي</t>
+        </is>
+      </c>
+      <c r="E109" s="5" t="inlineStr">
+        <is>
+          <t>ما العلاقة أو أوجه الشبه بين «الطبيب» و«الصيدلي»؟</t>
+        </is>
+      </c>
+      <c r="F109" s="5" t="inlineStr">
+        <is>
+          <t>1. علاقة تكامل لا تطابق: كلٌّ له دور مختلف في نفس المسار.</t>
+        </is>
+      </c>
+      <c r="G109" s="6" t="inlineStr">
+        <is>
+          <t>✔ الطبيب يشخص المرض والصيدلي يجهز الدواء (تكامل في العلاج)</t>
+        </is>
+      </c>
+      <c r="H109" s="5" t="inlineStr"/>
+    </row>
+    <row r="110" ht="156.2" customHeight="1">
+      <c r="A110" s="14" t="inlineStr">
+        <is>
+          <t>💭 التفكير المجرد — العلاقة بين الأشياء</t>
+        </is>
+      </c>
+      <c r="B110" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="C110" s="4" t="inlineStr">
+        <is>
+          <t>الهواء ↔ الحياة</t>
+        </is>
+      </c>
+      <c r="E110" s="5" t="inlineStr">
+        <is>
+          <t>ما العلاقة أو أوجه الشبه بين «الهواء» و«الحياة»؟</t>
+        </is>
+      </c>
+      <c r="F110" s="5" t="inlineStr">
+        <is>
+          <t>1. هذه علاقة «لزوم»: الهواء شرط للحياة.
+2. انتبه لترتيب الطرفين: الهواء شرط، الحياة مشروط.</t>
+        </is>
+      </c>
+      <c r="G110" s="6" t="inlineStr">
+        <is>
+          <t>✔ لا يمكن العيش بدون هواء (علاقة شرط)</t>
+        </is>
+      </c>
+      <c r="H110" s="5" t="inlineStr"/>
+    </row>
+    <row r="111" ht="156.2" customHeight="1">
+      <c r="A111" s="14" t="inlineStr">
+        <is>
+          <t>💭 التفكير المجرد — العلاقة بين الأشياء</t>
+        </is>
+      </c>
+      <c r="B111" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="C111" s="4" t="inlineStr">
+        <is>
+          <t>القطار ↔ الخريطة</t>
+        </is>
+      </c>
+      <c r="E111" s="5" t="inlineStr">
+        <is>
+          <t>ما العلاقة أو أوجه الشبه بين «القطار» و«الخريطة»؟</t>
+        </is>
+      </c>
+      <c r="F111" s="5" t="inlineStr">
+        <is>
+          <t>1. علاقة أداة بموضوعها: الخريطة أداة تخطيط لمسار القطار.</t>
+        </is>
+      </c>
+      <c r="G111" s="6" t="inlineStr">
+        <is>
+          <t>✔ الخريطة تستخدم لتحديد مسار القطار</t>
+        </is>
+      </c>
+      <c r="H111" s="5" t="inlineStr"/>
+    </row>
+    <row r="112" ht="156.2" customHeight="1">
+      <c r="A112" s="14" t="inlineStr">
+        <is>
+          <t>💭 التفكير المجرد — العلاقة بين الأشياء</t>
+        </is>
+      </c>
+      <c r="B112" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="C112" s="4" t="inlineStr">
+        <is>
+          <t>الرياضة ↔ الصحة</t>
+        </is>
+      </c>
+      <c r="E112" s="5" t="inlineStr">
+        <is>
+          <t>ما العلاقة أو أوجه الشبه بين «الرياضة» و«الصحة»؟</t>
+        </is>
+      </c>
+      <c r="F112" s="5" t="inlineStr">
+        <is>
+          <t>1. الرياضة سبب والصحة نتيجة.</t>
+        </is>
+      </c>
+      <c r="G112" s="6" t="inlineStr">
+        <is>
+          <t>✔ الرياضة تحافظ على الصحة وتقوي الجسم (علاقة سبب بنتيجة)</t>
+        </is>
+      </c>
+      <c r="H112" s="5" t="inlineStr"/>
+    </row>
+    <row r="113" ht="156.2" customHeight="1">
+      <c r="A113" s="14" t="inlineStr">
+        <is>
+          <t>💭 التفكير المجرد — العلاقة بين الأشياء</t>
+        </is>
+      </c>
+      <c r="B113" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="C113" s="4" t="inlineStr">
+        <is>
+          <t>العقل ↔ الكمبيوتر</t>
+        </is>
+      </c>
+      <c r="E113" s="5" t="inlineStr">
+        <is>
+          <t>ما العلاقة أو أوجه الشبه بين «العقل» و«الكمبيوتر»؟</t>
+        </is>
+      </c>
+      <c r="F113" s="5" t="inlineStr">
+        <is>
+          <t>1. الكمبيوتر محاكاة صناعية للعقل في المعالجة.</t>
+        </is>
+      </c>
+      <c r="G113" s="6" t="inlineStr">
+        <is>
+          <t>✔ كلاهما يعالج المعلومات ويتخذ قرارات</t>
+        </is>
+      </c>
+      <c r="H113" s="5" t="inlineStr"/>
+    </row>
+    <row r="114" ht="156.2" customHeight="1">
+      <c r="A114" s="14" t="inlineStr">
+        <is>
+          <t>💭 التفكير المجرد — العلاقة بين الأشياء</t>
+        </is>
+      </c>
+      <c r="B114" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="C114" s="4" t="inlineStr">
+        <is>
+          <t>الأمطار ↔ النباتات</t>
+        </is>
+      </c>
+      <c r="E114" s="5" t="inlineStr">
+        <is>
+          <t>ما العلاقة أو أوجه الشبه بين «الأمطار» و«النباتات»؟</t>
+        </is>
+      </c>
+      <c r="F114" s="5" t="inlineStr">
+        <is>
+          <t>1. المطر سبب والنمو نتيجة.</t>
+        </is>
+      </c>
+      <c r="G114" s="6" t="inlineStr">
+        <is>
+          <t>✔ الأمطار تساعد النباتات على النمو (سبب ← نتيجة)</t>
+        </is>
+      </c>
+      <c r="H114" s="5" t="inlineStr"/>
+    </row>
+    <row r="115" ht="156.2" customHeight="1">
+      <c r="A115" s="14" t="inlineStr">
+        <is>
+          <t>💭 التفكير المجرد — العلاقة بين الأشياء</t>
+        </is>
+      </c>
+      <c r="B115" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="C115" s="4" t="inlineStr">
+        <is>
+          <t>المرآة ↔ الصورة</t>
+        </is>
+      </c>
+      <c r="E115" s="5" t="inlineStr">
+        <is>
+          <t>ما العلاقة أو أوجه الشبه بين «المرآة» و«الصورة»؟</t>
+        </is>
+      </c>
+      <c r="F115" s="5" t="inlineStr">
+        <is>
+          <t>1. المرآة انعكاس مباشر والصورة انعكاس محفوظ.</t>
+        </is>
+      </c>
+      <c r="G115" s="6" t="inlineStr">
+        <is>
+          <t>✔ كلاهما يعكس الشكل الخارجي</t>
+        </is>
+      </c>
+      <c r="H115" s="5" t="inlineStr"/>
+    </row>
+    <row r="116" ht="156.2" customHeight="1">
+      <c r="A116" s="14" t="inlineStr">
+        <is>
+          <t>💭 التفكير المجرد — العلاقة بين الأشياء</t>
+        </is>
+      </c>
+      <c r="B116" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="C116" s="4" t="inlineStr">
+        <is>
+          <t>النجوم ↔ السماء</t>
+        </is>
+      </c>
+      <c r="E116" s="5" t="inlineStr">
+        <is>
+          <t>ما العلاقة أو أوجه الشبه بين «النجوم» و«السماء»؟</t>
+        </is>
+      </c>
+      <c r="F116" s="5" t="inlineStr">
+        <is>
+          <t>1. علاقة الجزء بالكل: النجم جزء من السماء.</t>
+        </is>
+      </c>
+      <c r="G116" s="6" t="inlineStr">
+        <is>
+          <t>✔ النجوم جزء من السماء وتضيئها ليلًا (علاقة جزء بكل)</t>
+        </is>
+      </c>
+      <c r="H116" s="5" t="inlineStr"/>
+    </row>
+    <row r="117" ht="100.04" customHeight="1">
+      <c r="A117" s="14" t="inlineStr">
+        <is>
+          <t>💭 التفكير المجرد — العلاقة بين الأشياء</t>
+        </is>
+      </c>
+      <c r="B117" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="C117" s="4" t="inlineStr">
+        <is>
+          <t>الجزر ↔ القرنبيط</t>
+        </is>
+      </c>
+      <c r="E117" s="5" t="inlineStr">
+        <is>
+          <t>ما العلاقة أو أوجه الشبه بين «الجزر» و«القرنبيط»؟</t>
+        </is>
+      </c>
+      <c r="F117" s="5" t="inlineStr">
+        <is>
+          <t>1. نوع واحد يجمعهما: الخضروات.
+2. «نبات» أعمّ وصحيح، لكن «خضروات» أدق إن وُجد.</t>
+        </is>
+      </c>
+      <c r="G117" s="6" t="inlineStr">
+        <is>
+          <t>✔ كلاهما خضروات (نباتات)</t>
+        </is>
+      </c>
+      <c r="H117" s="5" t="inlineStr"/>
+    </row>
+    <row r="118" ht="156.2" customHeight="1">
+      <c r="A118" s="14" t="inlineStr">
+        <is>
+          <t>💭 التفكير المجرد — العلاقة بين الأشياء</t>
+        </is>
+      </c>
+      <c r="B118" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="C118" s="4" t="inlineStr">
+        <is>
+          <t>الحديقة ↔ الميناء</t>
+        </is>
+      </c>
+      <c r="E118" s="5" t="inlineStr">
+        <is>
+          <t>ما العلاقة أو أوجه الشبه بين «الحديقة» و«الميناء»؟</t>
+        </is>
+      </c>
+      <c r="F118" s="5" t="inlineStr">
+        <is>
+          <t>1. الجامع: مساحة مفتوحة يستقبل فيها الناس أو البضائع.</t>
+        </is>
+      </c>
+      <c r="G118" s="6" t="inlineStr">
+        <is>
+          <t>✔ كلاهما مكان مفتوح</t>
+        </is>
+      </c>
+      <c r="H118" s="5" t="inlineStr"/>
+    </row>
+    <row r="119" ht="156.2" customHeight="1">
+      <c r="A119" s="14" t="inlineStr">
+        <is>
+          <t>💭 التفكير المجرد — العلاقة بين الأشياء</t>
+        </is>
+      </c>
+      <c r="B119" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="C119" s="4" t="inlineStr">
+        <is>
+          <t>الصديق ↔ العدو</t>
+        </is>
+      </c>
+      <c r="E119" s="5" t="inlineStr">
+        <is>
+          <t>ما العلاقة أو أوجه الشبه بين «الصديق» و«العدو»؟</t>
+        </is>
+      </c>
+      <c r="F119" s="5" t="inlineStr">
+        <is>
+          <t>1. علاقة تضاد في الموقف مع جامع «التأثير».</t>
+        </is>
+      </c>
+      <c r="G119" s="6" t="inlineStr">
+        <is>
+          <t>✔ كلاهما يؤثر في حياتك (وبينهما تضاد في الاتجاه)</t>
+        </is>
+      </c>
+      <c r="H119" s="5" t="inlineStr"/>
+    </row>
+    <row r="120" ht="100.04" customHeight="1">
+      <c r="A120" s="14" t="inlineStr">
+        <is>
+          <t>💭 التفكير المجرد — العلاقة بين الأشياء</t>
+        </is>
+      </c>
+      <c r="B120" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="C120" s="4" t="inlineStr">
+        <is>
+          <t>القرنبيط ↔ الخيار</t>
+        </is>
+      </c>
+      <c r="E120" s="5" t="inlineStr">
+        <is>
+          <t>ما العلاقة أو أوجه الشبه بين «القرنبيط» و«الخيار»؟</t>
+        </is>
+      </c>
+      <c r="F120" s="5" t="inlineStr">
+        <is>
+          <t>1. «أخضر» يصدق على الخيار فقط فاستبعده.</t>
+        </is>
+      </c>
+      <c r="G120" s="6" t="inlineStr">
+        <is>
+          <t>✔ كلاهما خضروات</t>
+        </is>
+      </c>
+      <c r="H120" s="5" t="inlineStr"/>
+    </row>
+    <row r="121" ht="156.2" customHeight="1">
+      <c r="A121" s="14" t="inlineStr">
+        <is>
+          <t>💭 التفكير المجرد — العلاقة بين الأشياء</t>
+        </is>
+      </c>
+      <c r="B121" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="C121" s="4" t="inlineStr">
+        <is>
+          <t>المد والجزر ↔ الإيقاع</t>
+        </is>
+      </c>
+      <c r="E121" s="5" t="inlineStr">
+        <is>
+          <t>ما العلاقة أو أوجه الشبه بين «المد والجزر» و«الإيقاع»؟</t>
+        </is>
+      </c>
+      <c r="F121" s="5" t="inlineStr">
+        <is>
+          <t>1. المد والجزر ظاهرة متكررة بإيقاع زمني.</t>
+        </is>
+      </c>
+      <c r="G121" s="6" t="inlineStr">
+        <is>
+          <t>✔ كلاهما له إيقاع (حركة متكررة منتظمة)</t>
+        </is>
+      </c>
+      <c r="H121" s="5" t="inlineStr"/>
+    </row>
+    <row r="122" ht="156.2" customHeight="1">
+      <c r="A122" s="14" t="inlineStr">
+        <is>
+          <t>💭 التفكير المجرد — العلاقة بين الأشياء</t>
+        </is>
+      </c>
+      <c r="B122" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="C122" s="4" t="inlineStr">
+        <is>
+          <t>سور المدرسة ↔ سور الحديقة</t>
+        </is>
+      </c>
+      <c r="E122" s="5" t="inlineStr">
+        <is>
+          <t>ما العلاقة أو أوجه الشبه بين «سور المدرسة» و«سور الحديقة»؟</t>
+        </is>
+      </c>
+      <c r="F122" s="5" t="inlineStr">
+        <is>
+          <t>1. الوظيفة هي المطلوبة لا الشكل.</t>
+        </is>
+      </c>
+      <c r="G122" s="6" t="inlineStr">
+        <is>
+          <t>✔ كلاهما يستخدم للحماية</t>
+        </is>
+      </c>
+      <c r="H122" s="5" t="inlineStr"/>
+    </row>
+    <row r="123" ht="156.2" customHeight="1">
+      <c r="A123" s="14" t="inlineStr">
+        <is>
+          <t>💭 التفكير المجرد — العلاقة بين الأشياء</t>
+        </is>
+      </c>
+      <c r="B123" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="C123" s="4" t="inlineStr">
+        <is>
+          <t>مرسى السفينة ↔ سور الحديقة</t>
+        </is>
+      </c>
+      <c r="E123" s="5" t="inlineStr">
+        <is>
+          <t>ما العلاقة أو أوجه الشبه بين «مرسى السفينة» و«سور الحديقة»؟</t>
+        </is>
+      </c>
+      <c r="F123" s="5" t="inlineStr">
+        <is>
+          <t>1. المرسى يحمي السفينة والسور يحمي الحديقة، وكلاهما يرسم حدًّا.</t>
+        </is>
+      </c>
+      <c r="G123" s="6" t="inlineStr">
+        <is>
+          <t>✔ كلاهما للحماية أو لتحديد الحدود</t>
+        </is>
+      </c>
+      <c r="H123" s="5" t="inlineStr"/>
+    </row>
+    <row r="124" ht="156.2" customHeight="1">
+      <c r="A124" s="14" t="inlineStr">
+        <is>
+          <t>💭 التفكير المجرد — العلاقة بين الأشياء</t>
+        </is>
+      </c>
+      <c r="B124" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="C124" s="4" t="inlineStr">
+        <is>
+          <t>الوسام ↔ الكأس</t>
+        </is>
+      </c>
+      <c r="E124" s="5" t="inlineStr">
+        <is>
+          <t>ما العلاقة أو أوجه الشبه بين «الوسام» و«الكأس»؟</t>
+        </is>
+      </c>
+      <c r="F124" s="5" t="inlineStr">
+        <is>
+          <t>1. ابدأ بالأدق: الغاية من الاثنين هي التكريم.
+2. فإن لم يكن موجودًا فالوصف: جائزتان.</t>
+        </is>
+      </c>
+      <c r="G124" s="6" t="inlineStr">
+        <is>
+          <t>✔ إن وُجد «للتكريم» فهو الأدق، وإلا فـ«كلاهما جائزتان»</t>
+        </is>
+      </c>
+      <c r="H124" s="5" t="inlineStr"/>
+    </row>
+    <row r="125" ht="156.2" customHeight="1">
+      <c r="A125" s="14" t="inlineStr">
+        <is>
+          <t>💭 التفكير المجرد — العلاقة بين الأشياء</t>
+        </is>
+      </c>
+      <c r="B125" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="C125" s="4" t="inlineStr">
+        <is>
+          <t>الطبلة ↔ البيانو</t>
+        </is>
+      </c>
+      <c r="E125" s="5" t="inlineStr">
+        <is>
+          <t>ما العلاقة أو أوجه الشبه بين «الطبلة» و«البيانو»؟</t>
+        </is>
+      </c>
+      <c r="F125" s="5" t="inlineStr">
+        <is>
+          <t>1. «يُضرب» يصدق على الطبلة فقط.</t>
+        </is>
+      </c>
+      <c r="G125" s="6" t="inlineStr">
+        <is>
+          <t>✔ كلاهما آلة موسيقية</t>
+        </is>
+      </c>
+      <c r="H125" s="5" t="inlineStr"/>
+    </row>
+    <row r="126" ht="156.2" customHeight="1">
+      <c r="A126" s="14" t="inlineStr">
+        <is>
+          <t>💭 التفكير المجرد — العلاقة بين الأشياء</t>
+        </is>
+      </c>
+      <c r="B126" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="C126" s="4" t="inlineStr">
+        <is>
+          <t>اللسان ↔ الأنف</t>
+        </is>
+      </c>
+      <c r="E126" s="5" t="inlineStr">
+        <is>
+          <t>ما العلاقة أو أوجه الشبه بين «اللسان» و«الأنف»؟</t>
+        </is>
+      </c>
+      <c r="F126" s="5" t="inlineStr">
+        <is>
+          <t>1. «للتذوق» يصدق على اللسان فقط فاستبعده.</t>
+        </is>
+      </c>
+      <c r="G126" s="6" t="inlineStr">
+        <is>
+          <t>✔ كلاهما جزء من الجسم أو عضو حسي (حسب الاختيارات)</t>
+        </is>
+      </c>
+      <c r="H126" s="5" t="inlineStr"/>
+    </row>
+    <row r="127" ht="148.4" customHeight="1">
+      <c r="A127" s="15" t="inlineStr">
+        <is>
+          <t>🗣️ العلاقات اللفظية (التناظر اللفظي)</t>
+        </is>
+      </c>
+      <c r="B127" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C127" s="4" t="inlineStr">
+        <is>
+          <t>حديقة : شجرة :: فصل : ؟</t>
+        </is>
+      </c>
+      <c r="E127" s="5" t="inlineStr">
+        <is>
+          <t>أكمل التناظر اللفظي: حديقة : شجرة  مثل  فصل : ...؟</t>
+        </is>
+      </c>
+      <c r="F127" s="5" t="inlineStr">
+        <is>
+          <t>1. العلاقة بين الزوج الأول: احتواء — الحديقة تحتوي على أشجار
+2. الحديقة مكان يحتوي على أشجار.
+3. إذن الفصل مكان يحتوي على طلاب.</t>
+        </is>
+      </c>
+      <c r="G127" s="6" t="inlineStr">
+        <is>
+          <t>✔ طالب</t>
+        </is>
+      </c>
+      <c r="H127" s="5" t="inlineStr">
+        <is>
+          <t>علاقة الاحتواء من أكثر ما يتكرر في الاختبارات.</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="148.4" customHeight="1">
+      <c r="A128" s="15" t="inlineStr">
+        <is>
+          <t>🗣️ العلاقات اللفظية (التناظر اللفظي)</t>
+        </is>
+      </c>
+      <c r="B128" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C128" s="4" t="inlineStr">
+        <is>
+          <t>سباحة : غرق :: قيادة : ؟</t>
+        </is>
+      </c>
+      <c r="E128" s="5" t="inlineStr">
+        <is>
+          <t>أكمل التناظر اللفظي: سباحة : غرق  مثل  قيادة : ...؟</t>
+        </is>
+      </c>
+      <c r="F128" s="5" t="inlineStr">
+        <is>
+          <t>1. العلاقة بين الزوج الأول: نشاط قد يؤدي إلى نتيجة سلبية محتملة
+2. السباحة نشاط قد ينتهي بالغرق.
+3. القيادة نشاط قد ينتهي بحادث.</t>
+        </is>
+      </c>
+      <c r="G128" s="6" t="inlineStr">
+        <is>
+          <t>✔ حادث</t>
+        </is>
+      </c>
+      <c r="H128" s="5" t="inlineStr"/>
+    </row>
+    <row r="129" ht="148.4" customHeight="1">
+      <c r="A129" s="15" t="inlineStr">
+        <is>
+          <t>🗣️ العلاقات اللفظية (التناظر اللفظي)</t>
+        </is>
+      </c>
+      <c r="B129" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C129" s="4" t="inlineStr">
+        <is>
+          <t>رؤية : بصيرة :: سماع : ؟</t>
+        </is>
+      </c>
+      <c r="E129" s="5" t="inlineStr">
+        <is>
+          <t>أكمل التناظر اللفظي: رؤية : بصيرة  مثل  سماع : ...؟</t>
+        </is>
+      </c>
+      <c r="F129" s="5" t="inlineStr">
+        <is>
+          <t>1. العلاقة بين الزوج الأول: حسي ⇄ معنوي — الرؤية تقابلها البصيرة
+2. الرؤية حاسة جسدية والبصيرة إدراك معنوي.
+3. إذن السماع حاسة والفهم إدراك معنوي.</t>
+        </is>
+      </c>
+      <c r="G129" s="6" t="inlineStr">
+        <is>
+          <t>✔ فهم</t>
+        </is>
+      </c>
+      <c r="H129" s="5" t="inlineStr"/>
+    </row>
+    <row r="130" ht="148.4" customHeight="1">
+      <c r="A130" s="15" t="inlineStr">
+        <is>
+          <t>🗣️ العلاقات اللفظية (التناظر اللفظي)</t>
+        </is>
+      </c>
+      <c r="B130" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C130" s="4" t="inlineStr">
+        <is>
+          <t>مكتبة : كتب :: حديقة : ؟</t>
+        </is>
+      </c>
+      <c r="E130" s="5" t="inlineStr">
+        <is>
+          <t>أكمل التناظر اللفظي: مكتبة : كتب  مثل  حديقة : ...؟</t>
+        </is>
+      </c>
+      <c r="F130" s="5" t="inlineStr">
+        <is>
+          <t>1. العلاقة بين الزوج الأول: مكان واحتواء — المكتبة تحتوي كتبًا
+2. المكتبة تحتوي كتبًا.
+3. الحديقة تحتوي زهورًا (أو أشجارًا حسب الخيارات).</t>
+        </is>
+      </c>
+      <c r="G130" s="6" t="inlineStr">
+        <is>
+          <t>✔ زهور</t>
+        </is>
+      </c>
+      <c r="H130" s="5" t="inlineStr"/>
+    </row>
+    <row r="131" ht="148.4" customHeight="1">
+      <c r="A131" s="15" t="inlineStr">
+        <is>
+          <t>🗣️ العلاقات اللفظية (التناظر اللفظي)</t>
+        </is>
+      </c>
+      <c r="B131" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C131" s="4" t="inlineStr">
+        <is>
+          <t>مقص : قص :: قلم : ؟</t>
+        </is>
+      </c>
+      <c r="E131" s="5" t="inlineStr">
+        <is>
+          <t>أكمل التناظر اللفظي: مقص : قص  مثل  قلم : ...؟</t>
+        </is>
+      </c>
+      <c r="F131" s="5" t="inlineStr">
+        <is>
+          <t>1. العلاقة بين الزوج الأول: الأداة ووظيفتها
+2. المقص أداة ووظيفته القص.
+3. القلم أداة ووظيفته الكتابة.</t>
+        </is>
+      </c>
+      <c r="G131" s="6" t="inlineStr">
+        <is>
+          <t>✔ كتابة</t>
+        </is>
+      </c>
+      <c r="H131" s="5" t="inlineStr"/>
+    </row>
+    <row r="132" ht="148.4" customHeight="1">
+      <c r="A132" s="15" t="inlineStr">
+        <is>
+          <t>🗣️ العلاقات اللفظية (التناظر اللفظي)</t>
+        </is>
+      </c>
+      <c r="B132" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C132" s="4" t="inlineStr">
+        <is>
+          <t>دراسة : نجاح :: نوم : ؟</t>
+        </is>
+      </c>
+      <c r="E132" s="5" t="inlineStr">
+        <is>
+          <t>أكمل التناظر اللفظي: دراسة : نجاح  مثل  نوم : ...؟</t>
+        </is>
+      </c>
+      <c r="F132" s="5" t="inlineStr">
+        <is>
+          <t>1. العلاقة بين الزوج الأول: سبب ← نتيجة
+2. الدراسة تؤدي إلى النجاح.
+3. النوم يؤدي إلى الراحة.</t>
+        </is>
+      </c>
+      <c r="G132" s="6" t="inlineStr">
+        <is>
+          <t>✔ راحة</t>
+        </is>
+      </c>
+      <c r="H132" s="5" t="inlineStr"/>
+    </row>
+    <row r="133" ht="148.4" customHeight="1">
+      <c r="A133" s="15" t="inlineStr">
+        <is>
+          <t>🗣️ العلاقات اللفظية (التناظر اللفظي)</t>
+        </is>
+      </c>
+      <c r="B133" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C133" s="4" t="inlineStr">
+        <is>
+          <t>ليل : نهار :: برد : ؟</t>
+        </is>
+      </c>
+      <c r="E133" s="5" t="inlineStr">
+        <is>
+          <t>أكمل التناظر اللفظي: ليل : نهار  مثل  برد : ...؟</t>
+        </is>
+      </c>
+      <c r="F133" s="5" t="inlineStr">
+        <is>
+          <t>1. العلاقة بين الزوج الأول: تضاد
+2. الليل ضد النهار.
+3. إذن البرد ضده الحرارة.</t>
+        </is>
+      </c>
+      <c r="G133" s="6" t="inlineStr">
+        <is>
+          <t>✔ حرارة</t>
+        </is>
+      </c>
+      <c r="H133" s="5" t="inlineStr">
+        <is>
+          <t>التضاد يُحل بمجرد النظر — لا تفكّر كثيرًا.</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="148.4" customHeight="1">
+      <c r="A134" s="15" t="inlineStr">
+        <is>
+          <t>🗣️ العلاقات اللفظية (التناظر اللفظي)</t>
+        </is>
+      </c>
+      <c r="B134" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C134" s="4" t="inlineStr">
+        <is>
+          <t>سعيد : مبتهج :: سريع : ؟</t>
+        </is>
+      </c>
+      <c r="E134" s="5" t="inlineStr">
+        <is>
+          <t>أكمل التناظر اللفظي: سعيد : مبتهج  مثل  سريع : ...؟</t>
+        </is>
+      </c>
+      <c r="F134" s="5" t="inlineStr">
+        <is>
+          <t>1. العلاقة بين الزوج الأول: ترادف
+2. سعيد = مبتهج (نفس المعنى).
+3. إذن سريع = خاطف.</t>
+        </is>
+      </c>
+      <c r="G134" s="6" t="inlineStr">
+        <is>
+          <t>✔ خاطف</t>
+        </is>
+      </c>
+      <c r="H134" s="5" t="inlineStr"/>
+    </row>
+    <row r="135" ht="148.4" customHeight="1">
+      <c r="A135" s="15" t="inlineStr">
+        <is>
+          <t>🗣️ العلاقات اللفظية (التناظر اللفظي)</t>
+        </is>
+      </c>
+      <c r="B135" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="C135" s="4" t="inlineStr">
+        <is>
+          <t>طائرة : مطار :: سفينة : ؟</t>
+        </is>
+      </c>
+      <c r="E135" s="5" t="inlineStr">
+        <is>
+          <t>أكمل التناظر اللفظي: طائرة : مطار  مثل  سفينة : ...؟</t>
+        </is>
+      </c>
+      <c r="F135" s="5" t="inlineStr">
+        <is>
+          <t>1. العلاقة بين الزوج الأول: الشيء ومكانه
+2. الطائرة مكانها المطار.
+3. السفينة مكانها الميناء.</t>
+        </is>
+      </c>
+      <c r="G135" s="6" t="inlineStr">
+        <is>
+          <t>✔ ميناء</t>
+        </is>
+      </c>
+      <c r="H135" s="5" t="inlineStr"/>
+    </row>
+    <row r="136" ht="148.4" customHeight="1">
+      <c r="A136" s="15" t="inlineStr">
+        <is>
+          <t>🗣️ العلاقات اللفظية (التناظر اللفظي)</t>
+        </is>
+      </c>
+      <c r="B136" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C136" s="4" t="inlineStr">
+        <is>
+          <t>مرض : دواء :: عطش : ؟</t>
+        </is>
+      </c>
+      <c r="E136" s="5" t="inlineStr">
+        <is>
+          <t>أكمل التناظر اللفظي: مرض : دواء  مثل  عطش : ...؟</t>
+        </is>
+      </c>
+      <c r="F136" s="5" t="inlineStr">
+        <is>
+          <t>1. العلاقة بين الزوج الأول: المشكلة وعلاجها
+2. المرض يعالجه الدواء.
+3. العطش يعالجه الماء.</t>
+        </is>
+      </c>
+      <c r="G136" s="6" t="inlineStr">
+        <is>
+          <t>✔ ماء</t>
+        </is>
+      </c>
+      <c r="H136" s="5" t="inlineStr"/>
+    </row>
+    <row r="137" ht="148.4" customHeight="1">
+      <c r="A137" s="15" t="inlineStr">
+        <is>
+          <t>🗣️ العلاقات اللفظية (التناظر اللفظي)</t>
+        </is>
+      </c>
+      <c r="B137" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="C137" s="4" t="inlineStr">
+        <is>
+          <t>كتاب : قراءة :: طعام : ؟</t>
+        </is>
+      </c>
+      <c r="E137" s="5" t="inlineStr">
+        <is>
+          <t>أكمل التناظر اللفظي: كتاب : قراءة  مثل  طعام : ...؟</t>
+        </is>
+      </c>
+      <c r="F137" s="5" t="inlineStr">
+        <is>
+          <t>1. العلاقة بين الزوج الأول: الشيء ونتيجته أو ما يُفعل به
+2. الكتاب نتيجته أن نقرأه.
+3. الطعام نتيجته أن نأكله.</t>
+        </is>
+      </c>
+      <c r="G137" s="6" t="inlineStr">
+        <is>
+          <t>✔ أكل</t>
+        </is>
+      </c>
+      <c r="H137" s="5" t="inlineStr">
+        <is>
+          <t>انتبه: «جوع» و«مضغ» و«مطبخ» كلها قريبة لكن الفعل المباشر هو الأكل.</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="148.4" customHeight="1">
+      <c r="A138" s="15" t="inlineStr">
+        <is>
+          <t>🗣️ العلاقات اللفظية (التناظر اللفظي)</t>
+        </is>
+      </c>
+      <c r="B138" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="C138" s="4" t="inlineStr">
+        <is>
+          <t>قلم : كاتب :: مطرقة : ؟</t>
+        </is>
+      </c>
+      <c r="E138" s="5" t="inlineStr">
+        <is>
+          <t>أكمل التناظر اللفظي: قلم : كاتب  مثل  مطرقة : ...؟</t>
+        </is>
+      </c>
+      <c r="F138" s="5" t="inlineStr">
+        <is>
+          <t>1. العلاقة بين الزوج الأول: الأداة ومَن يستخدمها
+2. القلم يستخدمه الكاتب.
+3. المطرقة يستخدمها النجار.</t>
+        </is>
+      </c>
+      <c r="G138" s="6" t="inlineStr">
+        <is>
+          <t>✔ نجار</t>
+        </is>
+      </c>
+      <c r="H138" s="5" t="inlineStr"/>
+    </row>
+    <row r="139" ht="148.4" customHeight="1">
+      <c r="A139" s="15" t="inlineStr">
+        <is>
+          <t>🗣️ العلاقات اللفظية (التناظر اللفظي)</t>
+        </is>
+      </c>
+      <c r="B139" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="C139" s="4" t="inlineStr">
+        <is>
+          <t>نار : دخان :: مرض : ؟</t>
+        </is>
+      </c>
+      <c r="E139" s="5" t="inlineStr">
+        <is>
+          <t>أكمل التناظر اللفظي: نار : دخان  مثل  مرض : ...؟</t>
+        </is>
+      </c>
+      <c r="F139" s="5" t="inlineStr">
+        <is>
+          <t>1. العلاقة بين الزوج الأول: الشيء وما ينتج عنه
+2. النار ينتج عنها دخان.
+3. المرض ينتج عنه أعراض — وهي الأشمل من الألم.</t>
+        </is>
+      </c>
+      <c r="G139" s="6" t="inlineStr">
+        <is>
+          <t>✔ أعراض</t>
+        </is>
+      </c>
+      <c r="H139" s="5" t="inlineStr">
+        <is>
+          <t>اختَر الأشمل عند تعدد النتائج.</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="148.4" customHeight="1">
+      <c r="A140" s="15" t="inlineStr">
+        <is>
+          <t>🗣️ العلاقات اللفظية (التناظر اللفظي)</t>
+        </is>
+      </c>
+      <c r="B140" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="C140" s="4" t="inlineStr">
+        <is>
+          <t>سمك : ماء :: طيور : ؟</t>
+        </is>
+      </c>
+      <c r="E140" s="5" t="inlineStr">
+        <is>
+          <t>أكمل التناظر اللفظي: سمك : ماء  مثل  طيور : ...؟</t>
+        </is>
+      </c>
+      <c r="F140" s="5" t="inlineStr">
+        <is>
+          <t>1. العلاقة بين الزوج الأول: الكائن وبيئته
+2. السمك يعيش في الماء.
+3. الطيور تعيش في الهواء — وهو الأعمّ.</t>
+        </is>
+      </c>
+      <c r="G140" s="6" t="inlineStr">
+        <is>
+          <t>✔ هواء</t>
+        </is>
+      </c>
+      <c r="H140" s="5" t="inlineStr"/>
+    </row>
+    <row r="141" ht="148.4" customHeight="1">
+      <c r="A141" s="15" t="inlineStr">
+        <is>
+          <t>🗣️ العلاقات اللفظية (التناظر اللفظي)</t>
+        </is>
+      </c>
+      <c r="B141" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="C141" s="4" t="inlineStr">
+        <is>
+          <t>مدرسة : تعليم :: مستشفى : ؟</t>
+        </is>
+      </c>
+      <c r="E141" s="5" t="inlineStr">
+        <is>
+          <t>أكمل التناظر اللفظي: مدرسة : تعليم  مثل  مستشفى : ...؟</t>
+        </is>
+      </c>
+      <c r="F141" s="5" t="inlineStr">
+        <is>
+          <t>1. العلاقة بين الزوج الأول: المكان ووظيفته
+2. المدرسة وظيفتها التعليم.
+3. المستشفى وظيفتها العلاج.</t>
+        </is>
+      </c>
+      <c r="G141" s="6" t="inlineStr">
+        <is>
+          <t>✔ علاج</t>
+        </is>
+      </c>
+      <c r="H141" s="5" t="inlineStr"/>
+    </row>
+    <row r="142" ht="148.4" customHeight="1">
+      <c r="A142" s="15" t="inlineStr">
+        <is>
+          <t>🗣️ العلاقات اللفظية (التناظر اللفظي)</t>
+        </is>
+      </c>
+      <c r="B142" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C142" s="4" t="inlineStr">
+        <is>
+          <t>عين : نظر :: أذن : ؟</t>
+        </is>
+      </c>
+      <c r="E142" s="5" t="inlineStr">
+        <is>
+          <t>أكمل التناظر اللفظي: عين : نظر  مثل  أذن : ...؟</t>
+        </is>
+      </c>
+      <c r="F142" s="5" t="inlineStr">
+        <is>
+          <t>1. العلاقة بين الزوج الأول: العضو ووظيفته
+2. العين وظيفتها النظر.
+3. الأذن وظيفتها السمع.</t>
+        </is>
+      </c>
+      <c r="G142" s="6" t="inlineStr">
+        <is>
+          <t>✔ سمع</t>
+        </is>
+      </c>
+      <c r="H142" s="5" t="inlineStr"/>
+    </row>
+    <row r="143" ht="148.4" customHeight="1">
+      <c r="A143" s="15" t="inlineStr">
+        <is>
+          <t>🗣️ العلاقات اللفظية (التناظر اللفظي)</t>
+        </is>
+      </c>
+      <c r="B143" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="C143" s="4" t="inlineStr">
+        <is>
+          <t>سيارة : طريق :: قطار : ؟</t>
+        </is>
+      </c>
+      <c r="E143" s="5" t="inlineStr">
+        <is>
+          <t>أكمل التناظر اللفظي: سيارة : طريق  مثل  قطار : ...؟</t>
+        </is>
+      </c>
+      <c r="F143" s="5" t="inlineStr">
+        <is>
+          <t>1. العلاقة بين الزوج الأول: المركبة ومسارها
+2. السيارة تسير على الطريق.
+3. القطار يسير على السكة الحديد — أما المحطة فمكان توقّفه.</t>
+        </is>
+      </c>
+      <c r="G143" s="6" t="inlineStr">
+        <is>
+          <t>✔ سكة حديد</t>
+        </is>
+      </c>
+      <c r="H143" s="5" t="inlineStr"/>
+    </row>
+    <row r="144" ht="148.4" customHeight="1">
+      <c r="A144" s="15" t="inlineStr">
+        <is>
+          <t>🗣️ العلاقات اللفظية (التناظر اللفظي)</t>
+        </is>
+      </c>
+      <c r="B144" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="C144" s="4" t="inlineStr">
+        <is>
+          <t>عسل : نحل :: بيض : ؟</t>
+        </is>
+      </c>
+      <c r="E144" s="5" t="inlineStr">
+        <is>
+          <t>أكمل التناظر اللفظي: عسل : نحل  مثل  بيض : ...؟</t>
+        </is>
+      </c>
+      <c r="F144" s="5" t="inlineStr">
+        <is>
+          <t>1. العلاقة بين الزوج الأول: المنتج ومصدره
+2. العسل يأتي من النحل.
+3. البيض يأتي من الدجاج — وهو الأدق من «طائر».</t>
+        </is>
+      </c>
+      <c r="G144" s="6" t="inlineStr">
+        <is>
+          <t>✔ دجاج</t>
+        </is>
+      </c>
+      <c r="H144" s="5" t="inlineStr"/>
+    </row>
+    <row r="145" ht="148.4" customHeight="1">
+      <c r="A145" s="15" t="inlineStr">
+        <is>
+          <t>🗣️ العلاقات اللفظية (التناظر اللفظي)</t>
+        </is>
+      </c>
+      <c r="B145" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="C145" s="4" t="inlineStr">
+        <is>
+          <t>كرة : لاعب :: فرشاة : ؟</t>
+        </is>
+      </c>
+      <c r="E145" s="5" t="inlineStr">
+        <is>
+          <t>أكمل التناظر اللفظي: كرة : لاعب  مثل  فرشاة : ...؟</t>
+        </is>
+      </c>
+      <c r="F145" s="5" t="inlineStr">
+        <is>
+          <t>1. العلاقة بين الزوج الأول: الأداة ومستخدمها (شخص)
+2. الكرة يستخدمها اللاعب.
+3. الفرشاة يستخدمها الرسام — والمطلوب «مَن» لا ماذا.</t>
+        </is>
+      </c>
+      <c r="G145" s="6" t="inlineStr">
+        <is>
+          <t>✔ رسام</t>
+        </is>
+      </c>
+      <c r="H145" s="5" t="inlineStr"/>
+    </row>
+    <row r="146" ht="148.4" customHeight="1">
+      <c r="A146" s="15" t="inlineStr">
+        <is>
+          <t>🗣️ العلاقات اللفظية (التناظر اللفظي)</t>
+        </is>
+      </c>
+      <c r="B146" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="C146" s="4" t="inlineStr">
+        <is>
+          <t>دواء : شفاء :: جوع : ؟</t>
+        </is>
+      </c>
+      <c r="E146" s="5" t="inlineStr">
+        <is>
+          <t>أكمل التناظر اللفظي: دواء : شفاء  مثل  جوع : ...؟</t>
+        </is>
+      </c>
+      <c r="F146" s="5" t="inlineStr">
+        <is>
+          <t>1. العلاقة بين الزوج الأول: ما يعالجه
+2. الدواء نتيجته الشفاء.
+3. الجوع يعالجه الطعام.</t>
+        </is>
+      </c>
+      <c r="G146" s="6" t="inlineStr">
+        <is>
+          <t>✔ طعام</t>
+        </is>
+      </c>
+      <c r="H146" s="5" t="inlineStr"/>
+    </row>
+    <row r="147" ht="148.4" customHeight="1">
+      <c r="A147" s="15" t="inlineStr">
+        <is>
+          <t>🗣️ العلاقات اللفظية (التناظر اللفظي)</t>
+        </is>
+      </c>
+      <c r="B147" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="C147" s="4" t="inlineStr">
+        <is>
+          <t>ورقة : كتاب :: طوبة : ؟</t>
+        </is>
+      </c>
+      <c r="E147" s="5" t="inlineStr">
+        <is>
+          <t>أكمل التناظر اللفظي: ورقة : كتاب  مثل  طوبة : ...؟</t>
+        </is>
+      </c>
+      <c r="F147" s="5" t="inlineStr">
+        <is>
+          <t>1. العلاقة بين الزوج الأول: جزء من كل
+2. الورقة جزء من الكتاب.
+3. الطوبة جزء من البيت.</t>
+        </is>
+      </c>
+      <c r="G147" s="6" t="inlineStr">
+        <is>
+          <t>✔ بيت</t>
+        </is>
+      </c>
+      <c r="H147" s="5" t="inlineStr"/>
+    </row>
+    <row r="148" ht="148.4" customHeight="1">
+      <c r="A148" s="15" t="inlineStr">
+        <is>
+          <t>🗣️ العلاقات اللفظية (التناظر اللفظي)</t>
+        </is>
+      </c>
+      <c r="B148" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="C148" s="4" t="inlineStr">
+        <is>
+          <t>قفل : مفتاح :: سؤال : ؟</t>
+        </is>
+      </c>
+      <c r="E148" s="5" t="inlineStr">
+        <is>
+          <t>أكمل التناظر اللفظي: قفل : مفتاح  مثل  سؤال : ...؟</t>
+        </is>
+      </c>
+      <c r="F148" s="5" t="inlineStr">
+        <is>
+          <t>1. العلاقة بين الزوج الأول: الشيء وما يفتحه أو يحلّه
+2. المفتاح يفتح القفل.
+3. الإجابة تحلّ السؤال.</t>
+        </is>
+      </c>
+      <c r="G148" s="6" t="inlineStr">
+        <is>
+          <t>✔ إجابة</t>
+        </is>
+      </c>
+      <c r="H148" s="5" t="inlineStr"/>
+    </row>
+    <row r="149" ht="148.4" customHeight="1">
+      <c r="A149" s="15" t="inlineStr">
+        <is>
+          <t>🗣️ العلاقات اللفظية (التناظر اللفظي)</t>
+        </is>
+      </c>
+      <c r="B149" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="C149" s="4" t="inlineStr">
+        <is>
+          <t>حليب : بقرة :: صوف : ؟</t>
+        </is>
+      </c>
+      <c r="E149" s="5" t="inlineStr">
+        <is>
+          <t>أكمل التناظر اللفظي: حليب : بقرة  مثل  صوف : ...؟</t>
+        </is>
+      </c>
+      <c r="F149" s="5" t="inlineStr">
+        <is>
+          <t>1. العلاقة بين الزوج الأول: المنتج ومصدره
+2. الحليب من البقرة.
+3. الصوف من الخروف.</t>
+        </is>
+      </c>
+      <c r="G149" s="6" t="inlineStr">
+        <is>
+          <t>✔ خروف</t>
+        </is>
+      </c>
+      <c r="H149" s="5" t="inlineStr"/>
+    </row>
+    <row r="150" ht="132.8" customHeight="1">
+      <c r="A150" s="16" t="inlineStr">
+        <is>
+          <t>📜 الأمثال الشعبية ولماذا نستخدم؟</t>
+        </is>
+      </c>
+      <c r="B150" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C150" s="4" t="inlineStr">
+        <is>
+          <t>«سقيع واحد لا يكفي»</t>
+        </is>
+      </c>
+      <c r="E150" s="5" t="inlineStr">
+        <is>
+          <t>سقيع واحد لا يكفي</t>
+        </is>
+      </c>
+      <c r="F150" s="5" t="inlineStr">
+        <is>
+          <t>1. اقرأ المثل حرفيًا: سقيع (برد) واحد لا يكفي وحده.
+2. ثم ترجمه إلى موقف: الحكم يحتاج أكثر من مرة واحدة.
+3. اختر المعنى المجازي الذي يشرح «لماذا نستخدم المثل».</t>
+        </is>
+      </c>
+      <c r="G150" s="6" t="inlineStr">
+        <is>
+          <t>✔ موقف واحد لا يكفي للحكم على الأمور</t>
+        </is>
+      </c>
+      <c r="H150" s="5" t="inlineStr"/>
+    </row>
+    <row r="151" ht="132.8" customHeight="1">
+      <c r="A151" s="16" t="inlineStr">
+        <is>
+          <t>📜 الأمثال الشعبية ولماذا نستخدم؟</t>
+        </is>
+      </c>
+      <c r="B151" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C151" s="4" t="inlineStr">
+        <is>
+          <t>«الأواني الفارغة تحدث ضجة أكثر»</t>
+        </is>
+      </c>
+      <c r="E151" s="5" t="inlineStr">
+        <is>
+          <t>الأواني الفارغة تحدث ضجة أكثر من المبتلاّة</t>
+        </is>
+      </c>
+      <c r="F151" s="5" t="inlineStr">
+        <is>
+          <t>1. الصورة: الإناء الفارغ يطنّ عند النقر عليه أكثر من الممتلئ.
+2. المعنى: الجاهل يتكلم كثيرًا والعالم قليل الكلام.</t>
+        </is>
+      </c>
+      <c r="G151" s="6" t="inlineStr">
+        <is>
+          <t>✔ الأشخاص الذين لا يعلمون شيئًا (أو لا يعرفون) هم أكثر الناس ضجيجًا</t>
+        </is>
+      </c>
+      <c r="H151" s="5" t="inlineStr"/>
+    </row>
+    <row r="152" ht="132.8" customHeight="1">
+      <c r="A152" s="16" t="inlineStr">
+        <is>
+          <t>📜 الأمثال الشعبية ولماذا نستخدم؟</t>
+        </is>
+      </c>
+      <c r="B152" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C152" s="4" t="inlineStr">
+        <is>
+          <t>«تفاحة واحدة فاسدة تفسد السلة كلها»</t>
+        </is>
+      </c>
+      <c r="E152" s="5" t="inlineStr">
+        <is>
+          <t>تفاحة واحدة فاسدة تفسد السلة كلها</t>
+        </is>
+      </c>
+      <c r="F152" s="5" t="inlineStr">
+        <is>
+          <t>1. المثل يُضرب للعنصر السيء الذي يؤثر على الجماعة.</t>
+        </is>
+      </c>
+      <c r="G152" s="6" t="inlineStr">
+        <is>
+          <t>✔ وجود شيء سيء أو فاسد في مجموعة ما قد يفسد المجموعة بأكملها</t>
+        </is>
+      </c>
+      <c r="H152" s="5" t="inlineStr"/>
+    </row>
+    <row r="153" ht="132.8" customHeight="1">
+      <c r="A153" s="16" t="inlineStr">
+        <is>
+          <t>📜 الأمثال الشعبية ولماذا نستخدم؟</t>
+        </is>
+      </c>
+      <c r="B153" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C153" s="4" t="inlineStr">
+        <is>
+          <t>«ليس كل ما يلمع ذهبًا»</t>
+        </is>
+      </c>
+      <c r="E153" s="5" t="inlineStr">
+        <is>
+          <t>ليس كل ما يلمع ذهبًا</t>
+        </is>
+      </c>
+      <c r="F153" s="5" t="inlineStr">
+        <is>
+          <t>1. القاعدة: احكم على الجوهر لا على المظهر.</t>
+        </is>
+      </c>
+      <c r="G153" s="6" t="inlineStr">
+        <is>
+          <t>✔ التحذير من الانخداع بالمظاهر — ليس كل ما يبدو لامعًا حقيقيًا أو نافعًا</t>
+        </is>
+      </c>
+      <c r="H153" s="5" t="inlineStr"/>
+    </row>
+    <row r="154" ht="132.8" customHeight="1">
+      <c r="A154" s="16" t="inlineStr">
+        <is>
+          <t>📜 الأمثال الشعبية ولماذا نستخدم؟</t>
+        </is>
+      </c>
+      <c r="B154" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C154" s="4" t="inlineStr">
+        <is>
+          <t>لماذا نغسل الملابس؟</t>
+        </is>
+      </c>
+      <c r="E154" s="5" t="inlineStr">
+        <is>
+          <t>لماذا نغسل الملابس؟</t>
+        </is>
+      </c>
+      <c r="F154" s="5" t="inlineStr">
+        <is>
+          <t>1. الغاية: التنظيف؛ والوسيلة: إزالة الأوساخ.
+2. إن وُجد الاختياران معًا فالغاية (للتنظيف) هي الأدق.</t>
+        </is>
+      </c>
+      <c r="G154" s="6" t="inlineStr">
+        <is>
+          <t>✔ للتنظيف — وإن لم يكن موجودًا فـ«لإزالة الأوساخ»</t>
+        </is>
+      </c>
+      <c r="H154" s="5" t="inlineStr"/>
+    </row>
+    <row r="155" ht="132.8" customHeight="1">
+      <c r="A155" s="16" t="inlineStr">
+        <is>
+          <t>📜 الأمثال الشعبية ولماذا نستخدم؟</t>
+        </is>
+      </c>
+      <c r="B155" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C155" s="4" t="inlineStr">
+        <is>
+          <t>لماذا نطهو الطعام؟</t>
+        </is>
+      </c>
+      <c r="E155" s="5" t="inlineStr">
+        <is>
+          <t>لماذا نطهو الطعام؟</t>
+        </is>
+      </c>
+      <c r="F155" s="5" t="inlineStr">
+        <is>
+          <t>1. الغاية: صلاحية الأكل؛ والنتيجة الفرعية: قتل الجراثيم.</t>
+        </is>
+      </c>
+      <c r="G155" s="6" t="inlineStr">
+        <is>
+          <t>✔ ليكون صالحًا للأكل — وإن لم يكن موجودًا فـ«لقتل الجراثيم»</t>
+        </is>
+      </c>
+      <c r="H155" s="5" t="inlineStr"/>
+    </row>
+    <row r="156" ht="49.5" customHeight="1">
+      <c r="A156" s="17" t="inlineStr">
+        <is>
+          <t>🔗 المتتابعات والمتسلسلة (نماذج حديثة)</t>
+        </is>
+      </c>
+      <c r="B156" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C156" s="4" t="inlineStr">
+        <is>
+          <t>فيبوناتشي: كل حد مجموع السابقين</t>
+        </is>
+      </c>
+      <c r="E156" s="5" t="inlineStr">
+        <is>
+          <t>أكمل المتتابعة:</t>
+        </is>
+      </c>
+      <c r="F156" s="5" t="inlineStr">
+        <is>
+          <t>1. 1 + 1 = 2، ثم 1 + 2 = 3، ثم 2 + 3 = 5.
+2. 3 + 5 = 8، و5 + 8 = 13.
+3. إذن 8 + 13 = 21.</t>
+        </is>
+      </c>
+      <c r="G156" s="6" t="inlineStr">
+        <is>
+          <t>✔ 21</t>
+        </is>
+      </c>
+      <c r="H156" s="5" t="inlineStr">
+        <is>
+          <t>فيبوناتشي أشهر متتالية في اختبارات IQ — احفظها.</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="78.5" customHeight="1">
+      <c r="A157" s="17" t="inlineStr">
+        <is>
+          <t>🔗 المتتابعات والمتسلسلة (نماذج حديثة)</t>
+        </is>
+      </c>
+      <c r="B157" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C157" s="4" t="inlineStr">
+        <is>
+          <t>معامل الضرب يتزايد (×2، ×3، ×4…)</t>
+        </is>
+      </c>
+      <c r="E157" s="5" t="inlineStr">
+        <is>
+          <t>أكمل المتتابعة:</t>
+        </is>
+      </c>
+      <c r="F157" s="5" t="inlineStr">
+        <is>
+          <t>1. 3 × 2 = 6.
+2. 6 × 3 = 18.
+3. 18 × 4 = 72.
+4. 72 × 5 = 360.
+5. إذن 360 × 6 = 2160.</t>
+        </is>
+      </c>
+      <c r="G157" s="6" t="inlineStr">
+        <is>
+          <t>✔ 2160</t>
+        </is>
+      </c>
+      <c r="H157" s="5" t="inlineStr"/>
+    </row>
+    <row r="158" ht="51.68" customHeight="1">
+      <c r="A158" s="17" t="inlineStr">
+        <is>
+          <t>🔗 المتتابعات والمتسلسلة (نماذج حديثة)</t>
+        </is>
+      </c>
+      <c r="B158" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C158" s="4" t="inlineStr">
+        <is>
+          <t>المربعات الكاملة</t>
+        </is>
+      </c>
+      <c r="E158" s="5" t="inlineStr">
+        <is>
+          <t>أكمل المتتابعة:</t>
+        </is>
+      </c>
+      <c r="F158" s="5" t="inlineStr">
+        <is>
+          <t>1. 1×1=1، 2×2=4، 3×3=9، 4×4=16، 5×5=25.
+2. إذن 6×6 = 36.</t>
+        </is>
+      </c>
+      <c r="G158" s="6" t="inlineStr">
+        <is>
+          <t>✔ 36</t>
+        </is>
+      </c>
+      <c r="H158" s="5" t="inlineStr">
+        <is>
+          <t>احفظ المربعات حتى 15² والمكعبات حتى 6³.</t>
+        </is>
+      </c>
+    </row>
+    <row r="159" ht="64" customHeight="1">
+      <c r="A159" s="17" t="inlineStr">
+        <is>
+          <t>🔗 المتتابعات والمتسلسلة (نماذج حديثة)</t>
+        </is>
+      </c>
+      <c r="B159" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C159" s="4" t="inlineStr">
+        <is>
+          <t>القسمة على 3</t>
+        </is>
+      </c>
+      <c r="E159" s="5" t="inlineStr">
+        <is>
+          <t>أكمل المتتابعة:</t>
+        </is>
+      </c>
+      <c r="F159" s="5" t="inlineStr">
+        <is>
+          <t>1. 81 ÷ 3 = 27.
+2. 27 ÷ 3 = 9.
+3. 9 ÷ 3 = 3.
+4. إذن 3 ÷ 3 = 1.</t>
+        </is>
+      </c>
+      <c r="G159" s="6" t="inlineStr">
+        <is>
+          <t>✔ 1</t>
+        </is>
+      </c>
+      <c r="H159" s="5" t="inlineStr"/>
+    </row>
+    <row r="160" ht="51.68" customHeight="1">
+      <c r="A160" s="17" t="inlineStr">
+        <is>
+          <t>🔗 المتتابعات والمتسلسلة (نماذج حديثة)</t>
+        </is>
+      </c>
+      <c r="B160" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C160" s="4" t="inlineStr">
+        <is>
+          <t>التضعيف المستمر</t>
+        </is>
+      </c>
+      <c r="E160" s="5" t="inlineStr">
+        <is>
+          <t>أكمل المتتابعة:</t>
+        </is>
+      </c>
+      <c r="F160" s="5" t="inlineStr">
+        <is>
+          <t>1. كل رقم = ضعف الذي قبله (×2).
+2. 2 × 80 = 160.</t>
+        </is>
+      </c>
+      <c r="G160" s="6" t="inlineStr">
+        <is>
+          <t>✔ 160</t>
+        </is>
+      </c>
+      <c r="H160" s="5" t="inlineStr"/>
+    </row>
+    <row r="161" ht="60.26000000000001" customHeight="1">
+      <c r="A161" s="17" t="inlineStr">
+        <is>
+          <t>🔗 المتتابعات والمتسلسلة (نماذج حديثة)</t>
+        </is>
+      </c>
+      <c r="B161" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C161" s="4" t="inlineStr">
+        <is>
+          <t>الزيادة نصف (كسر عشري)</t>
+        </is>
+      </c>
+      <c r="E161" s="5" t="inlineStr">
+        <is>
+          <t>أكمل المتتابعة:</t>
+        </is>
+      </c>
+      <c r="F161" s="5" t="inlineStr">
+        <is>
+          <t>1. الفرق بين كل حدين = 0.5 (نصف).
+2. 2.5 + 0.5 = 3.</t>
+        </is>
+      </c>
+      <c r="G161" s="6" t="inlineStr">
+        <is>
+          <t>✔ 3</t>
+        </is>
+      </c>
+      <c r="H161" s="5" t="inlineStr"/>
+    </row>
+    <row r="162" ht="60.26000000000001" customHeight="1">
+      <c r="A162" s="17" t="inlineStr">
+        <is>
+          <t>🔗 المتتابعات والمتسلسلة (نماذج حديثة)</t>
+        </is>
+      </c>
+      <c r="B162" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C162" s="4" t="inlineStr">
+        <is>
+          <t>النقص بمقدار 1.5</t>
+        </is>
+      </c>
+      <c r="E162" s="5" t="inlineStr">
+        <is>
+          <t>أكمل المتتابعة:</t>
+        </is>
+      </c>
+      <c r="F162" s="5" t="inlineStr">
+        <is>
+          <t>1. 10.5 − 9 = 1.5، و9 − 7.5 = 1.5، و7.5 − 6 = 1.5.
+2. إذن 6 − 1.5 = 4.5.</t>
+        </is>
+      </c>
+      <c r="G162" s="6" t="inlineStr">
+        <is>
+          <t>✔ 4.5</t>
+        </is>
+      </c>
+      <c r="H162" s="5" t="inlineStr"/>
+    </row>
+    <row r="163" ht="60.26000000000001" customHeight="1">
+      <c r="A163" s="17" t="inlineStr">
+        <is>
+          <t>🔗 المتتابعات والمتسلسلة (نماذج حديثة)</t>
+        </is>
+      </c>
+      <c r="B163" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C163" s="4" t="inlineStr">
+        <is>
+          <t>كسر عشري × 2</t>
+        </is>
+      </c>
+      <c r="E163" s="5" t="inlineStr">
+        <is>
+          <t>أكمل المتتابعة:</t>
+        </is>
+      </c>
+      <c r="F163" s="5" t="inlineStr">
+        <is>
+          <t>1. كل حد = ضعف الذي قبله: 1.2 × 2 = 2.4.
+2. 9.6 × 2 = 19.2.</t>
+        </is>
+      </c>
+      <c r="G163" s="6" t="inlineStr">
+        <is>
+          <t>✔ 19.2</t>
+        </is>
+      </c>
+      <c r="H163" s="5" t="inlineStr"/>
+    </row>
+    <row r="164" ht="93" customHeight="1">
+      <c r="A164" s="17" t="inlineStr">
+        <is>
+          <t>🔗 المتتابعات والمتسلسلة (نماذج حديثة)</t>
+        </is>
+      </c>
+      <c r="B164" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="C164" s="4" t="inlineStr">
+        <is>
+          <t>عشري: الصحيح ينقص 10 والكسر يزيد 0.1</t>
+        </is>
+      </c>
+      <c r="E164" s="5" t="inlineStr">
+        <is>
+          <t>أكمل المتتابعة:</t>
+        </is>
+      </c>
+      <c r="F164" s="5" t="inlineStr">
+        <is>
+          <t>1. حلّ الجزأين منفصلين: الصحيح 100 ← 90 ← 80 ← 70 ← 60 (ينقص 10).
+2. والكسر 0.1 ← 0.2 ← 0.3 ← 0.4 ← 0.5 (يزيد 0.1).
+3. إذن الناتج 60.5.
+4. أو بالفرق الثابت: 90.2 − 100.1 = −9.9، و80.3 − 90.2 = −9.9، فـ70.4 − 9.9 = 60.5.</t>
+        </is>
+      </c>
+      <c r="G164" s="6" t="inlineStr">
+        <is>
+          <t>✔ 60.5</t>
+        </is>
+      </c>
+      <c r="H164" s="5" t="inlineStr">
+        <is>
+          <t>تنبيه: ظهر في الفيديو الرقم (100.01) وهو خطأ مطبعي؛ الصحيح 100.1 ليستقيم الفرق 9.9.</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" ht="78.5" customHeight="1">
+      <c r="A165" s="17" t="inlineStr">
+        <is>
+          <t>🔗 المتتابعات والمتسلسلة (نماذج حديثة)</t>
+        </is>
+      </c>
+      <c r="B165" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C165" s="4" t="inlineStr">
+        <is>
+          <t>الزيادة تتزايد (+0.1، +0.2، +0.3…)</t>
+        </is>
+      </c>
+      <c r="E165" s="5" t="inlineStr">
+        <is>
+          <t>أكمل المتتابعة:</t>
+        </is>
+      </c>
+      <c r="F165" s="5" t="inlineStr">
+        <is>
+          <t>1. 1 + 0.1 = 1.1.
+2. 1.1 + 0.2 = 1.3.
+3. 1.3 + 0.3 = 1.6.
+4. 1.6 + 0.4 = 2.
+5. إذن 2 + 0.5 = 2.5.</t>
+        </is>
+      </c>
+      <c r="G165" s="6" t="inlineStr">
+        <is>
+          <t>✔ 2.5</t>
+        </is>
+      </c>
+      <c r="H165" s="5" t="inlineStr"/>
+    </row>
+    <row r="166" ht="64" customHeight="1">
+      <c r="A166" s="17" t="inlineStr">
+        <is>
+          <t>🔗 المتتابعات والمتسلسلة (نماذج حديثة)</t>
+        </is>
+      </c>
+      <c r="B166" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="C166" s="4" t="inlineStr">
+        <is>
+          <t>القاعدة المركّبة: × 2 ثم + 0.2</t>
+        </is>
+      </c>
+      <c r="E166" s="5" t="inlineStr">
+        <is>
+          <t>أكمل المتتابعة:</t>
+        </is>
+      </c>
+      <c r="F166" s="5" t="inlineStr">
+        <is>
+          <t>1. 5 × 2 = 10، ثم + 0.2 = 10.2.
+2. 10.2 × 2 = 20.4، ثم + 0.2 = 20.6.
+3. 20.6 × 2 = 41.2، ثم + 0.2 = 41.4.
+4. إذن 41.4 × 2 = 82.8، ثم + 0.2 = 83.</t>
+        </is>
+      </c>
+      <c r="G166" s="6" t="inlineStr">
+        <is>
+          <t>✔ 83</t>
+        </is>
+      </c>
+      <c r="H166" s="5" t="inlineStr">
+        <is>
+          <t>القاعدة المركّبة: اجمع خطوتين (ضرب ثم جمع) والتزم بهما في كل مرة.</t>
+        </is>
+      </c>
+    </row>
+    <row r="167" ht="73.52" customHeight="1">
+      <c r="A167" s="17" t="inlineStr">
+        <is>
+          <t>🔗 المتتابعات والمتسلسلة (نماذج حديثة)</t>
+        </is>
+      </c>
+      <c r="B167" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="C167" s="4" t="inlineStr">
+        <is>
+          <t>عشري كبير بفرق ثابت −29.8</t>
+        </is>
+      </c>
+      <c r="E167" s="5" t="inlineStr">
+        <is>
+          <t>أكمل المتتابعة:</t>
+        </is>
+      </c>
+      <c r="F167" s="5" t="inlineStr">
+        <is>
+          <t>1. الأرقام تتناقص إذن العملية طرح.
+2. 1971.4 − 1941.6 = 29.8، و1941.6 − 1911.8 = 29.8 — الفرق ثابت.
+3. إذن 1911.8 − 29.8 = 1882.</t>
+        </is>
+      </c>
+      <c r="G167" s="6" t="inlineStr">
+        <is>
+          <t>✔ 1882</t>
+        </is>
+      </c>
+      <c r="H167" s="5" t="inlineStr"/>
+    </row>
+    <row r="168" ht="156.2" customHeight="1">
+      <c r="A168" s="18" t="inlineStr">
+        <is>
+          <t>🧩 ألغاز الأشكال المركّبة (ورقة / سمكة / يد)</t>
+        </is>
+      </c>
+      <c r="B168" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C168" s="4" t="inlineStr">
+        <is>
+          <t>شيء نكتب به، بداخله طعام، وبخارجه شيء نرتديه</t>
+        </is>
+      </c>
+      <c r="E168" s="5" t="inlineStr">
+        <is>
+          <t>المثلث = سمكة، المربع = ورق، المعيّن = حذاء، الدائرة = يد. ارسم: شيء نكتب به، بداخله طعام، وبخارجه شيء نرتديه.</t>
+        </is>
+      </c>
+      <c r="F168" s="5" t="inlineStr">
+        <is>
+          <t>1. شيء نكتب به = اليد = الدائرة (هي الشكل الأوسط).
+2. بداخله طعام = السمكة = المثلث (أعمق شكل).
+3. بخارج شيء نكتب به شيء نرتديه = الحذاء = المعيّن (الشكل الخارجي).
+4. النتيجة من الخارج للداخل: معيّن ⊃ دائرة ⊃ مثلث.</t>
+        </is>
+      </c>
+      <c r="G168" s="6" t="inlineStr">
+        <is>
+          <t>✔ المعيّن (الحذاء) في الخارج، وبداخله الدائرة (اليد)، وبداخلها المثلث (السمكة)</t>
+        </is>
+      </c>
+      <c r="H168" s="5" t="inlineStr">
+        <is>
+          <t>الكلمة الفاصلة: «بداخله» = الشكل الأعمق، «يحيط به/بخارجه» = الشكل الأوسع.</t>
+        </is>
+      </c>
+    </row>
+    <row r="169" ht="156.2" customHeight="1">
+      <c r="A169" s="18" t="inlineStr">
+        <is>
+          <t>🧩 ألغاز الأشكال المركّبة (ورقة / سمكة / يد)</t>
+        </is>
+      </c>
+      <c r="B169" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C169" s="4" t="inlineStr">
+        <is>
+          <t>شيء نأكله، يحيط به شيء رقيق، وأسفله شيء نرتديه</t>
+        </is>
+      </c>
+      <c r="E169" s="5" t="inlineStr">
+        <is>
+          <t>ارسم: شيء نأكله، يحيط به شيء رقيق، وأسفله شيء نرتديه.</t>
+        </is>
+      </c>
+      <c r="F169" s="5" t="inlineStr">
+        <is>
+          <t>1. شيء نأكله = السمكة = المثلث (في القلب).
+2. يحيط به شيء رقيق = الورق = المربع (يحيط بالمثلث من كل جانب).
+3. أسفله شيء نرتديه = الحذاء = المعيّن (في الخارج).
+4. النتيجة: معيّن ⊃ مربع ⊃ مثلث.</t>
+        </is>
+      </c>
+      <c r="G169" s="6" t="inlineStr">
+        <is>
+          <t>✔ المعيّن (الحذاء) خارجًا، والمربع (الورق) في الوسط، والمثلث (السمكة) في القلب</t>
+        </is>
+      </c>
+      <c r="H169" s="5" t="inlineStr">
+        <is>
+          <t>لو تذكّر الترتيب «الأول ذُكر أولًا = الأعمق»، يصير الرسم ميكانيكيًا.</t>
+        </is>
+      </c>
+    </row>
+    <row r="170" ht="156.2" customHeight="1">
+      <c r="A170" s="18" t="inlineStr">
+        <is>
+          <t>🧩 ألغاز الأشكال المركّبة (ورقة / سمكة / يد)</t>
+        </is>
+      </c>
+      <c r="B170" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C170" s="4" t="inlineStr">
+        <is>
+          <t>شيء نكتب به، بداخله شيء نأكله، يحيط به شيء رقيق</t>
+        </is>
+      </c>
+      <c r="E170" s="5" t="inlineStr">
+        <is>
+          <t>ارسم: شيء نكتب به، بداخله شيء نأكله، يحيط به شيء رقيق.</t>
+        </is>
+      </c>
+      <c r="F170" s="5" t="inlineStr">
+        <is>
+          <t>1. شيء نكتب به = اليد = الدائرة.
+2. بداخله شيء نأكله = السمكة = المثلث (أعمق شكل).
+3. يحيط بالدائرة شيء رقيق = الورق = المربع (الشكل الخارجي).
+4. النتيجة: مربع ⊃ دائرة ⊃ مثلث.</t>
+        </is>
+      </c>
+      <c r="G170" s="6" t="inlineStr">
+        <is>
+          <t>✔ المربع (الورق) خارجًا، وبداخله الدائرة (اليد)، وبداخلها المثلث (السمكة)</t>
+        </is>
+      </c>
+      <c r="H170" s="5" t="inlineStr">
+        <is>
+          <t>أسهل أسئلة IQ على الإطلاق — لكن التركيز في «بداخله» و«يحيط به» هو كل شيء.</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" ht="122" customHeight="1">
+      <c r="A171" s="19" t="inlineStr">
+        <is>
+          <t>✂️ طي الورق والقص — نماذج إضافية</t>
+        </is>
+      </c>
+      <c r="B171" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C171" s="4" t="inlineStr">
+        <is>
+          <t>طيتان رأسيتان + قص زاوية ⇒ أربع قصّات</t>
+        </is>
+      </c>
+      <c r="E171" s="5" t="inlineStr">
+        <is>
+          <t>ورقة مستطيلة تُثنى نصفين ثم نصفين مرة ثانية (طيتان رأسيتان)، ثم يُقص مثلث من زاوية الربع. ما شكل الورقة بعد فردها؟</t>
+        </is>
+      </c>
+      <c r="F171" s="5" t="inlineStr">
+        <is>
+          <t>1. الطية الأولى تنصف الورقة، والثانية تنصفها مرة أخرى ⇒ أربعة أرباع متساوية.
+2. المثلث المقصوص من زاوية الربع سينعكس مرة مع كل طية ⇒ 2 × 2 = 4 مثلثات.
+3. تظهر القصّات الأربع على الحد العلوي للورقة بعد فردها: واحدة في كل ربع.
+4. طابق النتيجة مع الاختيارات — الشكل «ج» في الفيديو هو المطابق.</t>
+        </is>
+      </c>
+      <c r="G171" s="6" t="inlineStr">
+        <is>
+          <t>✔ أربعة مثلثات مقصوصة على الحد الأعلى، مثلث في كل ربع (الشكل ج كما في الفيديو)</t>
+        </is>
+      </c>
+      <c r="H171" s="5" t="inlineStr">
+        <is>
+          <t>عدد النسخ = 2^عدد الطيات: طيتان ⇒ أربع نسخ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="172" ht="78.5" customHeight="1">
+      <c r="A172" s="19" t="inlineStr">
+        <is>
+          <t>✂️ طي الورق والقص — نماذج إضافية</t>
+        </is>
+      </c>
+      <c r="B172" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C172" s="4" t="inlineStr">
+        <is>
+          <t>طية أفقية واحدة + قص من الأعلى ⇒ تناظر أفقي</t>
+        </is>
+      </c>
+      <c r="E172" s="5" t="inlineStr">
+        <is>
+          <t>ورقة مستطيلة تُثنى نصفين أفقيًّا (مرة واحدة)، ثم يُقص شريط من أعلاها. ما شكلها بعد الفرد؟</t>
+        </is>
+      </c>
+      <c r="F172" s="5" t="inlineStr">
+        <is>
+          <t>1. طية واحدة ⇒ نسختان من الشكل المقصوص.
+2. القص من أعلى القطعة المطوية ينعكس إلى أسفل الورقة بعد الفرد.
+3. فتظهر القصّة شريطًا في الأعلى وآخر مماثلًا في الأسفل (تناظر حول خط الطي).</t>
+        </is>
+      </c>
+      <c r="G172" s="6" t="inlineStr">
+        <is>
+          <t>✔ شريط مقصوص في الأعلى وآخر مقابل له في الأسفل (الشكل ج كما في الفيديو)</t>
+        </is>
+      </c>
+      <c r="H172" s="5" t="inlineStr">
+        <is>
+          <t>القاعدة العامة: القص من أعلى/أسفل ⇒ تناظر رأسي، والقص من اليمين/اليسار ⇒ تناظر أفقي.</t>
+        </is>
+      </c>
+    </row>
+    <row r="173" ht="78.5" customHeight="1">
+      <c r="A173" s="19" t="inlineStr">
+        <is>
+          <t>✂️ طي الورق والقص — نماذج إضافية</t>
+        </is>
+      </c>
+      <c r="B173" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C173" s="4" t="inlineStr">
+        <is>
+          <t>طية رأسية ثم أفقية + قص مربع من الزاوية ⇒ أربعة مربعات</t>
+        </is>
+      </c>
+      <c r="E173" s="5" t="inlineStr">
+        <is>
+          <t>ورقة تُثنى نصفين رأسيًّا ثم نصفين أفقيًّا، ثم يُقص مربع صغير من زاوية الربع. ما الشكل بعد الفرد؟</t>
+        </is>
+      </c>
+      <c r="F173" s="5" t="inlineStr">
+        <is>
+          <t>1. طيتان في اتجاهين مختلفين ⇒ أربعة أرباع (2 × 2).
+2. المربع المقصوص من الزاوية الخارجية يظهر في الأركان الأربعة للورقة.
+3. كل نسخة منعكسة أفقيًّا أو رأسيًّا عن جارتها، فتبدو متناظرة حول خطّي الطي.</t>
+        </is>
+      </c>
+      <c r="G173" s="6" t="inlineStr">
+        <is>
+          <t>✔ أربعة مربعات مقصوصة، واحد في كل ركن من أركان الورقة</t>
+        </is>
+      </c>
+      <c r="H173" s="5" t="inlineStr">
+        <is>
+          <t>حدّد أولًا: هل الطيتان في نفس الاتجاه (أربعة أعمدة) أم في اتجاهين (أربعة أرباع)؟</t>
+        </is>
+      </c>
+    </row>
+    <row r="174" ht="78.5" customHeight="1">
+      <c r="A174" s="19" t="inlineStr">
+        <is>
+          <t>✂️ طي الورق والقص — نماذج إضافية</t>
+        </is>
+      </c>
+      <c r="B174" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C174" s="4" t="inlineStr">
+        <is>
+          <t>طيتان رأسيتان + قص من حدّ الطية ⇒ شكل في المنتصف</t>
+        </is>
+      </c>
+      <c r="E174" s="5" t="inlineStr">
+        <is>
+          <t>ورقة تُثنى نصفين ثم نصفين (طيتان رأسيتان)، ثم يُقص نصف دائرة من حدّ الطية. ما الشكل بعد الفرد؟</t>
+        </is>
+      </c>
+      <c r="F174" s="5" t="inlineStr">
+        <is>
+          <t>1. القص على حدّ الطية ينعكس مع كل طية، فتتضاعف أنصاف الدوائر لتكوّن دوائر كاملة.
+2. الطية الأولى تعطي دائرة كاملة عند خط المنتصف الأول.
+3. الطية الثانية تنقل المشهد إلى النصف الآخر ⇒ دائرتان كاملتان على خطوط الطي.</t>
+        </is>
+      </c>
+      <c r="G174" s="6" t="inlineStr">
+        <is>
+          <t>✔ دائرتان كاملتان مقصوصتان على خطّي الطي (في ثلثَي الورقة)</t>
+        </is>
+      </c>
+      <c r="H174" s="5" t="inlineStr">
+        <is>
+          <t>القص من «نص الورقة» (حدّ الطية) ينتج شكلًا مزدوجًا — لا نصف شكل.</t>
+        </is>
+      </c>
+    </row>
+    <row r="175" ht="78.5" customHeight="1">
+      <c r="A175" s="19" t="inlineStr">
+        <is>
+          <t>✂️ طي الورق والقص — نماذج إضافية</t>
+        </is>
+      </c>
+      <c r="B175" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C175" s="4" t="inlineStr">
+        <is>
+          <t>طية رأسية وأفقية + نصف دائرة على الطية ⇒ دائرتان رأسيتان</t>
+        </is>
+      </c>
+      <c r="E175" s="5" t="inlineStr">
+        <is>
+          <t>ورقة تُثنى رأسيًّا ثم أفقيًّا، ثم يُقص نصف دائرة من حدّ الطية الرأسية. ما الشكل بعد الفرد؟</t>
+        </is>
+      </c>
+      <c r="F175" s="5" t="inlineStr">
+        <is>
+          <t>1. نصف الدائرة على الطية الرأسية يصير دائرة كاملة عند الفرد الأول.
+2. الطية الأفقية تنقل الدائرة إلى النصف السفلي.
+3. النتيجة: دائرتان كاملتان فوق بعضهما في منتصف الورقة رأسيًّا.</t>
+        </is>
+      </c>
+      <c r="G175" s="6" t="inlineStr">
+        <is>
+          <t>✔ دائرتان كاملتان في منتصف الورقة، واحدة فوق الأخرى</t>
+        </is>
+      </c>
+      <c r="H175" s="5" t="inlineStr"/>
+    </row>
+    <row r="176" ht="78.5" customHeight="1">
+      <c r="A176" s="19" t="inlineStr">
+        <is>
+          <t>✂️ طي الورق والقص — نماذج إضافية</t>
+        </is>
+      </c>
+      <c r="B176" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C176" s="4" t="inlineStr">
+        <is>
+          <t>طيتان رأسيتان + قص مربع من الزاوية السفلية</t>
+        </is>
+      </c>
+      <c r="E176" s="5" t="inlineStr">
+        <is>
+          <t>ورقة تُثنى نصفين ثم نصفين (طيتان رأسيتان)، ثم يُقص مربع من الزاوية. كيف تظهر القصّات بعد الفرد؟</t>
+        </is>
+      </c>
+      <c r="F176" s="5" t="inlineStr">
+        <is>
+          <t>1. أربع نسخ من المربع (2 × 2).
+2. كل نسخة في ربع، وتتجاور النسخ على خطوط الطي فتكوّن في المنتصف شكلًا مزدوجًا متماسكًا.
+3. النتيجة: أربعة مربعات على الحد، يندمج كل اثنين منها عند خط الطي.</t>
+        </is>
+      </c>
+      <c r="G176" s="6" t="inlineStr">
+        <is>
+          <t>✔ أربعة مربعات مقصوصة على الحد، يندمج كل متجاورين عند خطّي الطي</t>
+        </is>
+      </c>
+      <c r="H176" s="5" t="inlineStr">
+        <is>
+          <t>عند القص من حدّ الطية تتلامس النسخ، وعند القص من الحدود الخارجية تتباعد.</t>
+        </is>
+      </c>
+    </row>
+    <row r="177" ht="194.5" customHeight="1">
+      <c r="A177" s="20" t="inlineStr">
+        <is>
+          <t>🔲 مصفوفات متقدمة (قاعدة الأعمدة / الأقطار / التكرار)</t>
+        </is>
+      </c>
+      <c r="B177" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C177" s="4" t="inlineStr">
+        <is>
+          <t>قاعدة الصفوف: نفس المجموعة تتكرر في كل صف</t>
+        </is>
+      </c>
+      <c r="E177" s="5" t="inlineStr">
+        <is>
+          <t>كل صف يحتوي على ثلاث خلايا، وفي كل خلية ثلاثة أشكال. الخلية الثالثة (على اليسار) في كل صف ناقصها شكل واحد — أكمل الأشكال الثلاثة الناقصة.</t>
+        </is>
+      </c>
+      <c r="F177" s="5" t="inlineStr">
+        <is>
+          <t>1. لا تبحث عن تتابع بين الصفوف: احسب «مجموعة الأشكال» في خلايا الصف الواحد.
+2. الصف الأول: كل خلية فيها نفس الثلاثة (مثلث أسود + مربع أبيض + دائرة سوداء) بترتيب مختلف ⇒ الناقص هو المثلث الأسود.
+3. الصف الثاني: كل خلية فيها (دائرتان + مربع أسود) ⇒ الناقص هو الدائرة المقلّمة.
+4. الصف الثالث: كل خلية فيها (مثلث مقلّم + مربع أسود + دائرة مقلّمة) ⇒ الناقص المثلث المقلّم.
+5. تحقق بالأعمدة: أول خلية في كل صف تعطي (3 مختلفين، دائرتين + مربع، 3 مختلفين) — وهو نفس نمط الخلايا الباقية.
+6. النتيجة: مثلث أسود + دائرة مقلّمة + مثلث مقلّم ⇒ الاختيار 1.</t>
+        </is>
+      </c>
+      <c r="G177" s="6" t="inlineStr">
+        <is>
+          <t>✔ الاختيار 1 — مثلث أسود في الصف الأول، دائرة مقلّمة في الثاني، مثلث مقلّم في الثالث</t>
+        </is>
+      </c>
+      <c r="H177" s="5" t="inlineStr">
+        <is>
+          <t>سرّ هذا النوع: لا تتابع بين الصفوف بل «نفس المجموعة تتكرر» — اجمع الأشكال كمجموعة وقارن.</t>
+        </is>
+      </c>
+    </row>
+    <row r="178" ht="156.2" customHeight="1">
+      <c r="A178" s="20" t="inlineStr">
+        <is>
+          <t>🔲 مصفوفات متقدمة (قاعدة الأعمدة / الأقطار / التكرار)</t>
+        </is>
+      </c>
+      <c r="B178" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C178" s="4" t="inlineStr">
+        <is>
+          <t>شكل منسا الصعب — الحل على الأقطار</t>
+        </is>
+      </c>
+      <c r="E178" s="5" t="inlineStr">
+        <is>
+          <t>رقّم المربعات من 1 إلى 9 (من اليمين لليسار، صفًّا بصفٍّ). المربع 9 ناقص — ما الشكل الصحيح؟</t>
+        </is>
+      </c>
+      <c r="F178" s="5" t="inlineStr">
+        <is>
+          <t>1. لا تعمل بالصفوف والأعمدة هنا — الشكل يُحل بالأقطار (النمط المائل).
+2. القطر الأول (3، 5، 7): المثلث المخطط فوق في 3 ⇒ نزل تحت في 5 ⇒ رجع فوق في 7.
+3. القطر الثاني (6، 8، 1): نفس القاعدة — ما فوق ينزل تحت وما تحت يطلع فوق.
+4. القطر الثالث (2، 4، 9): في 2 المخطط تحت والفاضي فوق، وفي 4 انعكس (المخطط فوق)، إذن في 9 يعود كما في 2.
+5. النتيجة: مثلث فوق فاضي + مثلث تحت مخطط.</t>
+        </is>
+      </c>
+      <c r="G178" s="6" t="inlineStr">
+        <is>
+          <t>✔ الاختيار E — مثلث فوق فارغ ومثلث تحت مخطط</t>
+        </is>
+      </c>
+      <c r="H178" s="5" t="inlineStr">
+        <is>
+          <t>الشكل صعب ويحتاج وقتًا؛ احفظ صورته وطريقته (الأقطار) إن ظهر لك في الامتحان.</t>
+        </is>
+      </c>
+    </row>
+    <row r="179" ht="156.2" customHeight="1">
+      <c r="A179" s="20" t="inlineStr">
+        <is>
+          <t>🔲 مصفوفات متقدمة (قاعدة الأعمدة / الأقطار / التكرار)</t>
+        </is>
+      </c>
+      <c r="B179" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C179" s="4" t="inlineStr">
+        <is>
+          <t>قاعدة التكرار: الوحدات الثلاثية والرباعية تتكرر</t>
+        </is>
+      </c>
+      <c r="E179" s="5" t="inlineStr">
+        <is>
+          <t>لا يوجد تتابع بين الصفوف ولا الأعمدة. ما الشكل الذي يملأ المربع الناقص؟</t>
+        </is>
+      </c>
+      <c r="F179" s="5" t="inlineStr">
+        <is>
+          <t>1. جرّب الصفوف والأعمدة أولًا — لن تجد أي تتابع، فهذا الشكل يُحل بملاحظة التكرار.
+2. لاحظ أن وحدات الثلاثة أشكال تتكرر بنفس التشكيل (واحد فوق واثنان تحت) في أكثر من مربع.
+3. كذلك وحدات الأربعة أشكال تتكرر بنفس التشكيل (مربع 2×2).
+4. أما الوحدات المفردة والمزدوجة فلا تتكرر، فلا تُبنَى عليها النتيجة.
+5. إذن المربع الناقص يكرر تشكيل الثلاثة أشكال ⇒ الاختيار «د».</t>
+        </is>
+      </c>
+      <c r="G179" s="6" t="inlineStr">
+        <is>
+          <t>✔ الاختيار «د» — تشكيل الثلاثة أشكال (واحد فوق واثنان تحت)</t>
+        </is>
+      </c>
+      <c r="H179" s="5" t="inlineStr">
+        <is>
+          <t>حين يفشل التتابع: ابحث عن «ما يتكرر» — التكرار نفسه هو القاعدة.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H89"/>
+  <autoFilter ref="A1:H179"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
@@ -5997,7 +11319,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -6007,404 +11329,1024 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="14" t="inlineStr">
+      <c r="A1" s="21" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B1" s="14" t="inlineStr">
+      <c r="B1" s="21" t="inlineStr">
         <is>
           <t>عنوان الفيديو</t>
         </is>
       </c>
-      <c r="C1" s="14" t="inlineStr">
+      <c r="C1" s="21" t="inlineStr">
         <is>
           <t>المحور</t>
         </is>
       </c>
-      <c r="D1" s="14" t="inlineStr">
+      <c r="D1" s="21" t="inlineStr">
         <is>
           <t>الرابط</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="n">
+      <c r="A2" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="16" t="inlineStr">
-        <is>
-          <t>بأسهل طرق الحل - الأشكال المتطابقة والمماثلة وتدوير الأشكال</t>
-        </is>
-      </c>
-      <c r="C2" s="17" t="inlineStr">
-        <is>
-          <t>الأشكال المتطابقة</t>
-        </is>
-      </c>
-      <c r="D2" s="18" t="inlineStr">
+      <c r="B2" s="23" t="inlineStr">
+        <is>
+          <t>بسهولة شرح أسئلة IQ (نسبة الذكاء) - الجزء الأول</t>
+        </is>
+      </c>
+      <c r="C2" s="24" t="inlineStr">
+        <is>
+          <t>مصفوفات وأشكال</t>
+        </is>
+      </c>
+      <c r="D2" s="25" t="inlineStr">
+        <is>
+          <t>https://youtu.be/V_zkkehBvbQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="23" t="inlineStr">
+        <is>
+          <t>بسهولة شرح أسئلة IQ - الشكل المكمل - الجزء الثاني</t>
+        </is>
+      </c>
+      <c r="C3" s="24" t="inlineStr">
+        <is>
+          <t>الشكل المكمل</t>
+        </is>
+      </c>
+      <c r="D3" s="25" t="inlineStr">
+        <is>
+          <t>https://youtu.be/wtUI5X2ppjs</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="23" t="inlineStr">
+        <is>
+          <t>بسهولة شرح أسئلة IQ - الجزء الثاني</t>
+        </is>
+      </c>
+      <c r="C4" s="24" t="inlineStr">
+        <is>
+          <t>أشكال متنوعة</t>
+        </is>
+      </c>
+      <c r="D4" s="25" t="inlineStr">
+        <is>
+          <t>https://youtu.be/bjytZM1dJOw</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="23" t="inlineStr">
+        <is>
+          <t>بسهولة شرح أسئلة IQ (المكعبات) - الجزء الرابع</t>
+        </is>
+      </c>
+      <c r="C5" s="24" t="inlineStr">
+        <is>
+          <t>المكعبات</t>
+        </is>
+      </c>
+      <c r="D5" s="25" t="inlineStr">
+        <is>
+          <t>https://youtu.be/4Qk4AJJp7Yo</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>بسهولة شرح أسئلة IQ (المصفوفات) - الجزء الخامس</t>
+        </is>
+      </c>
+      <c r="C6" s="24" t="inlineStr">
+        <is>
+          <t>المصفوفات</t>
+        </is>
+      </c>
+      <c r="D6" s="25" t="inlineStr">
+        <is>
+          <t>https://youtu.be/hfRxRoU8OFY</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="23" t="inlineStr">
+        <is>
+          <t>بسهولة شرح أسئلة IQ (المرايا وثني الورق) - الجزء السادس</t>
+        </is>
+      </c>
+      <c r="C7" s="24" t="inlineStr">
+        <is>
+          <t>المرايا وثني الورق</t>
+        </is>
+      </c>
+      <c r="D7" s="25" t="inlineStr">
+        <is>
+          <t>https://youtu.be/MDt1D3NzB24</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="22" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="23" t="inlineStr">
+        <is>
+          <t>بسهولة شرح أسئلة IQ (تعبيرات الوجه) - الجزء السابع</t>
+        </is>
+      </c>
+      <c r="C8" s="24" t="inlineStr">
+        <is>
+          <t>تعبيرات الوجه</t>
+        </is>
+      </c>
+      <c r="D8" s="25" t="inlineStr">
+        <is>
+          <t>https://youtu.be/Ouyv9RTYXHQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="22" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="23" t="inlineStr">
+        <is>
+          <t>شرح أسئلة IQ (الأسئلة المقالية) - الجزء الثامن</t>
+        </is>
+      </c>
+      <c r="C9" s="24" t="inlineStr">
+        <is>
+          <t>الأسئلة المقالية</t>
+        </is>
+      </c>
+      <c r="D9" s="25" t="inlineStr">
+        <is>
+          <t>https://youtu.be/5t8OAwQMEFk</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="22" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="23" t="inlineStr">
+        <is>
+          <t>حل IQ اختبار تدوير الأشكال - اختبار بيردو للتصور المكاني</t>
+        </is>
+      </c>
+      <c r="C10" s="24" t="inlineStr">
+        <is>
+          <t>التصور المكاني</t>
+        </is>
+      </c>
+      <c r="D10" s="25" t="inlineStr">
+        <is>
+          <t>https://youtu.be/D9kUXTcia4A</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="23" t="inlineStr">
+        <is>
+          <t>أحدث أسئلة IQ - المتسلسلة - المتتاليات - المتواليات</t>
+        </is>
+      </c>
+      <c r="C11" s="24" t="inlineStr">
+        <is>
+          <t>المتتاليات</t>
+        </is>
+      </c>
+      <c r="D11" s="25" t="inlineStr">
+        <is>
+          <t>https://youtu.be/-x_B02vr9QY</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="22" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t>شرح أحدث أسئلة IQ - حل أشكال X, Y, Z بسهولة</t>
+        </is>
+      </c>
+      <c r="C12" s="24" t="inlineStr">
+        <is>
+          <t>تركيب الأشكال</t>
+        </is>
+      </c>
+      <c r="D12" s="25" t="inlineStr">
+        <is>
+          <t>https://youtu.be/2Ihx_bTZzTU</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="22" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="23" t="inlineStr">
+        <is>
+          <t>شرح متتاليات بالكسور العشرية</t>
+        </is>
+      </c>
+      <c r="C13" s="24" t="inlineStr">
+        <is>
+          <t>الكسور العشرية</t>
+        </is>
+      </c>
+      <c r="D13" s="25" t="inlineStr">
+        <is>
+          <t>https://youtu.be/3uY8YdcW0ic</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="22" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="23" t="inlineStr">
+        <is>
+          <t>متتاليات الحروف - أحدث أسئلة IQ</t>
+        </is>
+      </c>
+      <c r="C14" s="24" t="inlineStr">
+        <is>
+          <t>متتاليات الحروف</t>
+        </is>
+      </c>
+      <c r="D14" s="25" t="inlineStr">
+        <is>
+          <t>https://youtu.be/cAIyFyMa7VY</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="22" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="23" t="inlineStr">
+        <is>
+          <t>IQ - شرح أسئلة تركيب الأشكال بمعلومية X , Y , Z</t>
+        </is>
+      </c>
+      <c r="C15" s="24" t="inlineStr">
+        <is>
+          <t>تركيب الأشكال</t>
+        </is>
+      </c>
+      <c r="D15" s="25" t="inlineStr">
+        <is>
+          <t>https://youtu.be/5jx2zlqbyC8</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="22" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="23" t="inlineStr">
+        <is>
+          <t>شرح أحدث أشكال IQ - وردت بالفعل في الاختبارات</t>
+        </is>
+      </c>
+      <c r="C16" s="24" t="inlineStr">
+        <is>
+          <t>أشكال حديثة</t>
+        </is>
+      </c>
+      <c r="D16" s="25" t="inlineStr">
+        <is>
+          <t>https://youtu.be/YoEJZqi61CM</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="22" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="23" t="inlineStr">
+        <is>
+          <t>حل أشكال IQ الحديثة التي وردت بالفعل خلال الفترة السابقة</t>
+        </is>
+      </c>
+      <c r="C17" s="24" t="inlineStr">
+        <is>
+          <t>أشكال حديثة</t>
+        </is>
+      </c>
+      <c r="D17" s="25" t="inlineStr">
+        <is>
+          <t>https://youtu.be/2oSouwEyWZE</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="22" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="23" t="inlineStr">
+        <is>
+          <t>شرح أحدث أسئلة IQ بسهولة - تخصص لغة عربية 2024</t>
+        </is>
+      </c>
+      <c r="C18" s="24" t="inlineStr">
+        <is>
+          <t>مراجعة مطولة</t>
+        </is>
+      </c>
+      <c r="D18" s="25" t="inlineStr">
+        <is>
+          <t>https://youtu.be/H7oXyOwewpM</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="22" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="23" t="inlineStr">
+        <is>
+          <t>أحدث أسئلة IQ (طي الورق) وردت بالفعل في الاختبارات</t>
+        </is>
+      </c>
+      <c r="C19" s="24" t="inlineStr">
+        <is>
+          <t>طي الورق</t>
+        </is>
+      </c>
+      <c r="D19" s="25" t="inlineStr">
+        <is>
+          <t>https://youtu.be/i6nL9sjz-Dw</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="22" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="23" t="inlineStr">
+        <is>
+          <t>شرح أحدث أسئلة IQ - المتتابعات والمتسلسلة</t>
+        </is>
+      </c>
+      <c r="C20" s="24" t="inlineStr">
+        <is>
+          <t>المتتابعات</t>
+        </is>
+      </c>
+      <c r="D20" s="25" t="inlineStr">
+        <is>
+          <t>https://youtu.be/RIMlB-lU3Zs</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="22" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="23" t="inlineStr">
+        <is>
+          <t>أحدث أشكال نسبة الذكاء IQ وردت بالفعل - 2025</t>
+        </is>
+      </c>
+      <c r="C21" s="24" t="inlineStr">
+        <is>
+          <t>أشكال 2025</t>
+        </is>
+      </c>
+      <c r="D21" s="25" t="inlineStr">
+        <is>
+          <t>https://youtu.be/fE9INmOeuGs</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="23" t="inlineStr">
+        <is>
+          <t>شرح أحدث أسئلة IQ - ورقة سمكة يد (ألغاز الأشكال)</t>
+        </is>
+      </c>
+      <c r="C22" s="24" t="inlineStr">
+        <is>
+          <t>ألغاز الأشكال</t>
+        </is>
+      </c>
+      <c r="D22" s="25" t="inlineStr">
+        <is>
+          <t>https://youtu.be/pZWlqSyV5qA</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="22" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="23" t="inlineStr">
+        <is>
+          <t>شرح أسئلة ونماذج الميزان من محور IQ</t>
+        </is>
+      </c>
+      <c r="C23" s="24" t="inlineStr">
+        <is>
+          <t>الميزان</t>
+        </is>
+      </c>
+      <c r="D23" s="25" t="inlineStr">
+        <is>
+          <t>https://youtu.be/x7G9D552NRc</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="22" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="23" t="inlineStr">
+        <is>
+          <t>أحدث أسئلة IQ - العلاقة بين الأشياء (الشوكة والملعقة...)</t>
+        </is>
+      </c>
+      <c r="C24" s="24" t="inlineStr">
+        <is>
+          <t>العلاقة بين الأشياء</t>
+        </is>
+      </c>
+      <c r="D24" s="25" t="inlineStr">
+        <is>
+          <t>https://youtu.be/lpjD8DxhEKk</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="22" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="23" t="inlineStr">
+        <is>
+          <t>شرح أسئلة IQ - الأمثال الشعبية ولماذا نستخدم؟</t>
+        </is>
+      </c>
+      <c r="C25" s="24" t="inlineStr">
+        <is>
+          <t>الأمثال الشعبية</t>
+        </is>
+      </c>
+      <c r="D25" s="25" t="inlineStr">
+        <is>
+          <t>https://youtu.be/YtyenRbHXkA</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="22" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="23" t="inlineStr">
+        <is>
+          <t>أسهل طريقة لحل طي المكعبات - المكعبات المفرودة</t>
+        </is>
+      </c>
+      <c r="C26" s="24" t="inlineStr">
+        <is>
+          <t>طي المكعبات</t>
+        </is>
+      </c>
+      <c r="D26" s="25" t="inlineStr">
+        <is>
+          <t>https://youtu.be/VhTX7E_XJNA</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="22" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="23" t="inlineStr">
+        <is>
+          <t>أسهل طريقة لحل IQ - استخرج الشكل الخاطئ للمكعبات</t>
+        </is>
+      </c>
+      <c r="C27" s="24" t="inlineStr">
+        <is>
+          <t>استراتيجية عقارب الساعة</t>
+        </is>
+      </c>
+      <c r="D27" s="25" t="inlineStr">
+        <is>
+          <t>https://youtu.be/tR_-va2vlmA</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="22" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="23" t="inlineStr">
+        <is>
+          <t>بأسهل طرق الحل - دليلك الشامل لحل طي المكعبات</t>
+        </is>
+      </c>
+      <c r="C28" s="24" t="inlineStr">
+        <is>
+          <t>طي المكعبات</t>
+        </is>
+      </c>
+      <c r="D28" s="25" t="inlineStr">
+        <is>
+          <t>https://youtu.be/nq1hV7tput0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="22" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="23" t="inlineStr">
+        <is>
+          <t>شرح أحدث أسئلة المتتاليات (المتتابعات) من محور IQ</t>
+        </is>
+      </c>
+      <c r="C29" s="24" t="inlineStr">
+        <is>
+          <t>المتتاليات</t>
+        </is>
+      </c>
+      <c r="D29" s="25" t="inlineStr">
+        <is>
+          <t>https://youtu.be/PUF2tQlIJFk</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="22" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="23" t="inlineStr">
+        <is>
+          <t>مراجعة ما قبل الامتحان - العلاقة بين الأشياء - الأمثال</t>
+        </is>
+      </c>
+      <c r="C30" s="24" t="inlineStr">
+        <is>
+          <t>التفكير المجرد</t>
+        </is>
+      </c>
+      <c r="D30" s="25" t="inlineStr">
+        <is>
+          <t>https://youtu.be/NFJ627OHhfQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="23" t="inlineStr">
+        <is>
+          <t>أحدث أسئلة IQ العلاقات اللفظية - وردت بالفعل</t>
+        </is>
+      </c>
+      <c r="C31" s="24" t="inlineStr">
+        <is>
+          <t>العلاقات اللفظية</t>
+        </is>
+      </c>
+      <c r="D31" s="25" t="inlineStr">
+        <is>
+          <t>https://youtu.be/dz-sE6m2qfg</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="22" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="23" t="inlineStr">
+        <is>
+          <t>بسهولة حل أسئلة IQ - المكعبات والعلاقة بين الأشياء</t>
+        </is>
+      </c>
+      <c r="C32" s="24" t="inlineStr">
+        <is>
+          <t>مراجعة</t>
+        </is>
+      </c>
+      <c r="D32" s="25" t="inlineStr">
+        <is>
+          <t>https://youtu.be/CR5hlBRX6Go</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="22" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="23" t="inlineStr">
+        <is>
+          <t>أحدث أسئلة في IQ - طريقة حل أسئلة نسبة الذكاء 2026</t>
+        </is>
+      </c>
+      <c r="C33" s="24" t="inlineStr">
+        <is>
+          <t>مراجعة 2026</t>
+        </is>
+      </c>
+      <c r="D33" s="25" t="inlineStr">
+        <is>
+          <t>https://youtu.be/XbokmztXcuw</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="22" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="23" t="inlineStr">
+        <is>
+          <t>أحدث أسئلة في IQ - مراجعة ما قبل الامتحان</t>
+        </is>
+      </c>
+      <c r="C34" s="24" t="inlineStr">
+        <is>
+          <t>مراجعة</t>
+        </is>
+      </c>
+      <c r="D34" s="25" t="inlineStr">
+        <is>
+          <t>https://youtu.be/SoeGN11cUAQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="22" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="23" t="inlineStr">
+        <is>
+          <t>حل أحدث مسألة من أشكال IQ بطريقة سهلة وبسيطة</t>
+        </is>
+      </c>
+      <c r="C35" s="24" t="inlineStr">
+        <is>
+          <t>مصفوفة أشكال</t>
+        </is>
+      </c>
+      <c r="D35" s="25" t="inlineStr">
+        <is>
+          <t>https://youtu.be/oIpba1Dz4OY</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="22" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="23" t="inlineStr">
+        <is>
+          <t>أحدث أسئلة في IQ - لجميع الوظائف 2025</t>
+        </is>
+      </c>
+      <c r="C36" s="24" t="inlineStr">
+        <is>
+          <t>مراجعة 2025</t>
+        </is>
+      </c>
+      <c r="D36" s="25" t="inlineStr">
+        <is>
+          <t>https://youtu.be/kK_LDGJVMwU</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="22" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="23" t="inlineStr">
+        <is>
+          <t>أحدث أشكال IQ وردت بالفعل - مسابقة الأزهر الشريف</t>
+        </is>
+      </c>
+      <c r="C37" s="24" t="inlineStr">
+        <is>
+          <t>الأزهر</t>
+        </is>
+      </c>
+      <c r="D37" s="25" t="inlineStr">
+        <is>
+          <t>https://youtu.be/zapEEiuKolw</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="22" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="23" t="inlineStr">
+        <is>
+          <t>شرح ومراجعة IQ - الأشكال المماثلة - العلاقات - تدوير المكعب</t>
+        </is>
+      </c>
+      <c r="C38" s="24" t="inlineStr">
+        <is>
+          <t>مراجعة</t>
+        </is>
+      </c>
+      <c r="D38" s="25" t="inlineStr">
+        <is>
+          <t>https://youtu.be/h_d5Q6PTVPk</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="22" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="23" t="inlineStr">
+        <is>
+          <t>التناظر اللفظي في IQ - العلاقة بين الكلمات</t>
+        </is>
+      </c>
+      <c r="C39" s="24" t="inlineStr">
+        <is>
+          <t>التناظر اللفظي</t>
+        </is>
+      </c>
+      <c r="D39" s="25" t="inlineStr">
+        <is>
+          <t>https://youtu.be/rdee9dRkE7g</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="22" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="23" t="inlineStr">
+        <is>
+          <t>أحدث أسئلة وردت بالفعل في IQ - المماثل + المرايا + المتتاليات</t>
+        </is>
+      </c>
+      <c r="C40" s="24" t="inlineStr">
+        <is>
+          <t>مراجعة</t>
+        </is>
+      </c>
+      <c r="D40" s="25" t="inlineStr">
+        <is>
+          <t>https://youtu.be/3zT0e7wN5Jw</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="22" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="23" t="inlineStr">
+        <is>
+          <t>حل أحدث أسئلة IQ والتفكير المنطقي - 2026</t>
+        </is>
+      </c>
+      <c r="C41" s="24" t="inlineStr">
+        <is>
+          <t>تفكير منطقي</t>
+        </is>
+      </c>
+      <c r="D41" s="25" t="inlineStr">
+        <is>
+          <t>https://youtu.be/Nm4w4T-SQ4U</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="22" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="23" t="inlineStr">
+        <is>
+          <t>أحدث أشكال IQ - مسابقة الطب البيطري</t>
+        </is>
+      </c>
+      <c r="C42" s="24" t="inlineStr">
+        <is>
+          <t>الطب البيطري</t>
+        </is>
+      </c>
+      <c r="D42" s="25" t="inlineStr">
+        <is>
+          <t>https://youtu.be/BVUNf8AFYHU</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="22" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="23" t="inlineStr">
+        <is>
+          <t>أحدث أشكال IQ - تركيب الأشكال XYZ - المتماثلة 2026</t>
+        </is>
+      </c>
+      <c r="C43" s="24" t="inlineStr">
+        <is>
+          <t>مراجعة 2026</t>
+        </is>
+      </c>
+      <c r="D43" s="25" t="inlineStr">
+        <is>
+          <t>https://youtu.be/68GlrljDVXk</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="22" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="23" t="inlineStr">
+        <is>
+          <t>شرح أحدث أشكال IQ - تخصص الدراسات بمسابقة الحصة</t>
+        </is>
+      </c>
+      <c r="C44" s="24" t="inlineStr">
+        <is>
+          <t>تخصص الدراسات</t>
+        </is>
+      </c>
+      <c r="D44" s="25" t="inlineStr">
+        <is>
+          <t>https://youtu.be/rXsi_P42sBA</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="22" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="23" t="inlineStr">
+        <is>
+          <t>شكل IQ من (منسا) حيّر الجميع - أحدث أشكال IQ</t>
+        </is>
+      </c>
+      <c r="C45" s="24" t="inlineStr">
+        <is>
+          <t>شكل منسا</t>
+        </is>
+      </c>
+      <c r="D45" s="25" t="inlineStr">
+        <is>
+          <t>https://youtu.be/0bz1oMT6zq0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="22" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="23" t="inlineStr">
+        <is>
+          <t>حل أكثر من 10 أشكال IQ من أصعب الأشكال</t>
+        </is>
+      </c>
+      <c r="C46" s="24" t="inlineStr">
+        <is>
+          <t>أشكال صعبة</t>
+        </is>
+      </c>
+      <c r="D46" s="25" t="inlineStr">
+        <is>
+          <t>https://youtu.be/OmU6XDh_peI</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="22" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="23" t="inlineStr">
+        <is>
+          <t>أحدث أنماط IQ - تخصص اللغة الإنجليزية 2026</t>
+        </is>
+      </c>
+      <c r="C47" s="24" t="inlineStr">
+        <is>
+          <t>أنماط 2026</t>
+        </is>
+      </c>
+      <c r="D47" s="25" t="inlineStr">
+        <is>
+          <t>https://youtu.be/qm-HIrolrQI</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="22" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="23" t="inlineStr">
+        <is>
+          <t>أحدث 10 أشكال IQ - الأزهر والأحساء 2026</t>
+        </is>
+      </c>
+      <c r="C48" s="24" t="inlineStr">
+        <is>
+          <t>مراجعة 2026</t>
+        </is>
+      </c>
+      <c r="D48" s="25" t="inlineStr">
+        <is>
+          <t>https://youtu.be/Cz-tTLKItEc</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="22" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="23" t="inlineStr">
+        <is>
+          <t>أهم 20 شكل IQ وردت بالفعل في اختبارات التوظيف</t>
+        </is>
+      </c>
+      <c r="C49" s="24" t="inlineStr">
+        <is>
+          <t>20 شكلًا</t>
+        </is>
+      </c>
+      <c r="D49" s="25" t="inlineStr">
+        <is>
+          <t>https://youtu.be/LYWSbDP100o</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="22" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="23" t="inlineStr">
+        <is>
+          <t>مسابقة الخبراء - أهم أنماط IQ وردت بالفعل</t>
+        </is>
+      </c>
+      <c r="C50" s="24" t="inlineStr">
+        <is>
+          <t>مسابقة الخبراء</t>
+        </is>
+      </c>
+      <c r="D50" s="25" t="inlineStr">
+        <is>
+          <t>https://youtu.be/yOJd0tAVxIk</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="22" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="23" t="inlineStr">
+        <is>
+          <t>بأسهل طرق الحل - المتطابقة والمماثلة وتدوير الأشكال</t>
+        </is>
+      </c>
+      <c r="C51" s="24" t="inlineStr">
+        <is>
+          <t>المتطابقة والمماثلة</t>
+        </is>
+      </c>
+      <c r="D51" s="25" t="inlineStr">
         <is>
           <t>https://youtu.be/pmDaEsMNvkI</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="16" t="inlineStr">
-        <is>
-          <t>حل اختبار في جميع المحاور (كفايات سلوكية - IQ - معلومات عامة)</t>
-        </is>
-      </c>
-      <c r="C3" s="17" t="inlineStr">
-        <is>
-          <t>اختبار شامل</t>
-        </is>
-      </c>
-      <c r="D3" s="18" t="inlineStr">
-        <is>
-          <t>https://youtu.be/Sg94ye-k5Tc</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="16" t="inlineStr">
-        <is>
-          <t>دليلك الشامل لحل طي المكعبات</t>
-        </is>
-      </c>
-      <c r="C4" s="17" t="inlineStr">
-        <is>
-          <t>طي المكعبات</t>
-        </is>
-      </c>
-      <c r="D4" s="18" t="inlineStr">
-        <is>
-          <t>https://youtu.be/nq1hV7tput0</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="16" t="inlineStr">
-        <is>
-          <t>أحدث أشكال IQ وردت بالاختبارات 2026</t>
-        </is>
-      </c>
-      <c r="C5" s="17" t="inlineStr">
-        <is>
-          <t>أشكال 2026</t>
-        </is>
-      </c>
-      <c r="D5" s="18" t="inlineStr">
-        <is>
-          <t>https://youtu.be/68GlrljDVXk</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="15" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>اختبار بيردو للتصور المكاني</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr">
-        <is>
-          <t>التصور المكاني</t>
-        </is>
-      </c>
-      <c r="D6" s="18" t="inlineStr">
-        <is>
-          <t>https://youtu.be/D9kUXTcia4A</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="15" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>شرح أسئلة IQ - الجزء الأول</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr">
-        <is>
-          <t>مصفوفات الأشكال</t>
-        </is>
-      </c>
-      <c r="D7" s="18" t="inlineStr">
-        <is>
-          <t>https://youtu.be/V_zkkehBvbQ</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="15" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>شرح أسئلة IQ - الجزء الثاني (الشكل المكمل)</t>
-        </is>
-      </c>
-      <c r="C8" s="17" t="inlineStr">
-        <is>
-          <t>الشكل المكمل</t>
-        </is>
-      </c>
-      <c r="D8" s="18" t="inlineStr">
-        <is>
-          <t>https://youtu.be/wtUI5X2ppjs</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="15" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>شرح أسئلة IQ - الجزء الثاني (تتمة)</t>
-        </is>
-      </c>
-      <c r="C9" s="17" t="inlineStr">
-        <is>
-          <t>تتمة الأشكال</t>
-        </is>
-      </c>
-      <c r="D9" s="18" t="inlineStr">
-        <is>
-          <t>https://youtu.be/bjytZM1dJOw</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="15" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>شرح أسئلة IQ (المكعبات) - الجزء الرابع</t>
-        </is>
-      </c>
-      <c r="C10" s="17" t="inlineStr">
-        <is>
-          <t>المكعبات</t>
-        </is>
-      </c>
-      <c r="D10" s="18" t="inlineStr">
-        <is>
-          <t>https://youtu.be/4Qk4AJJp7Yo</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="15" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>شرح أسئلة IQ (المصفوفات) - الجزء الخامس</t>
-        </is>
-      </c>
-      <c r="C11" s="17" t="inlineStr">
-        <is>
-          <t>المصفوفات</t>
-        </is>
-      </c>
-      <c r="D11" s="18" t="inlineStr">
-        <is>
-          <t>https://youtu.be/hfRxRoU8OFY</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="15" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>شرح أسئلة IQ (المرايا وثني الورق) - الجزء السادس</t>
-        </is>
-      </c>
-      <c r="C12" s="17" t="inlineStr">
-        <is>
-          <t>المرايا</t>
-        </is>
-      </c>
-      <c r="D12" s="18" t="inlineStr">
-        <is>
-          <t>https://youtu.be/MDt1D3NzB24</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="15" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
-        <is>
-          <t>شرح أسئلة IQ (تعبيرات الوجه) - الجزء السابع</t>
-        </is>
-      </c>
-      <c r="C13" s="17" t="inlineStr">
-        <is>
-          <t>تعبيرات الوجه</t>
-        </is>
-      </c>
-      <c r="D13" s="18" t="inlineStr">
-        <is>
-          <t>https://youtu.be/Ouyv9RTYXHQ</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="15" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>شرح أسئلة IQ - الجزء الثامن (الأسئلة المقالية)</t>
-        </is>
-      </c>
-      <c r="C14" s="17" t="inlineStr">
-        <is>
-          <t>الأسئلة المقالية</t>
-        </is>
-      </c>
-      <c r="D14" s="18" t="inlineStr">
-        <is>
-          <t>https://youtu.be/5t8OAwQMEFk</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="15" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
-        <is>
-          <t>أحدث أسئلة IQ - المتتاليات والمتسلسلات</t>
-        </is>
-      </c>
-      <c r="C15" s="17" t="inlineStr">
-        <is>
-          <t>المتتاليات</t>
-        </is>
-      </c>
-      <c r="D15" s="18" t="inlineStr">
-        <is>
-          <t>https://youtu.be/-x_B02vr9QY</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="15" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="16" t="inlineStr">
-        <is>
-          <t>متتاليات الحروف</t>
-        </is>
-      </c>
-      <c r="C16" s="17" t="inlineStr">
-        <is>
-          <t>الحروف</t>
-        </is>
-      </c>
-      <c r="D16" s="18" t="inlineStr">
-        <is>
-          <t>https://youtu.be/cAIyFyMa7VY</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="15" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
-        <is>
-          <t>متتاليات بالكسور العشرية</t>
-        </is>
-      </c>
-      <c r="C17" s="17" t="inlineStr">
-        <is>
-          <t>الكسور العشرية</t>
-        </is>
-      </c>
-      <c r="D17" s="18" t="inlineStr">
-        <is>
-          <t>https://youtu.be/3uY8YdcW0ic</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="15" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
-        <is>
-          <t>تركيب الأشكال X, Y, Z</t>
-        </is>
-      </c>
-      <c r="C18" s="17" t="inlineStr">
-        <is>
-          <t>تركيب الأشكال</t>
-        </is>
-      </c>
-      <c r="D18" s="18" t="inlineStr">
-        <is>
-          <t>https://youtu.be/2Ihx_bTZzTU</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="15" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
-        <is>
-          <t>تركيب الأشكال بمعلومية X , Y , Z (2)</t>
-        </is>
-      </c>
-      <c r="C19" s="17" t="inlineStr">
-        <is>
-          <t>تركيب الأشكال</t>
-        </is>
-      </c>
-      <c r="D19" s="18" t="inlineStr">
-        <is>
-          <t>https://youtu.be/5jx2zlqbyC8</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="15" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" s="16" t="inlineStr">
-        <is>
-          <t>أحدث أشكال نسبة الذكاء IQ وردت بالفعل</t>
-        </is>
-      </c>
-      <c r="C20" s="17" t="inlineStr">
-        <is>
-          <t>أشكال حديثة</t>
-        </is>
-      </c>
-      <c r="D20" s="18" t="inlineStr">
-        <is>
-          <t>https://youtu.be/fE9INmOeuGs</t>
         </is>
       </c>
     </row>
@@ -6429,6 +12371,37 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D18" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D19" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D51" r:id="rId50"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6449,192 +12422,192 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="19" t="inlineStr">
+      <c r="A1" s="26" t="inlineStr">
         <is>
           <t>اليوم</t>
         </is>
       </c>
-      <c r="B1" s="19" t="inlineStr">
+      <c r="B1" s="26" t="inlineStr">
         <is>
           <t>الموضوع</t>
         </is>
       </c>
-      <c r="C1" s="19" t="inlineStr">
+      <c r="C1" s="26" t="inlineStr">
         <is>
           <t>المطلوب</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="20" t="inlineStr">
+      <c r="A2" s="27" t="inlineStr">
         <is>
           <t>اليوم 1</t>
         </is>
       </c>
-      <c r="B2" s="21" t="inlineStr">
+      <c r="B2" s="28" t="inlineStr">
         <is>
           <t>المتتاليات + المصفوفات الرقمية</t>
         </is>
       </c>
-      <c r="C2" s="21" t="inlineStr">
+      <c r="C2" s="28" t="inlineStr">
         <is>
           <t>احفظ أنماط الفروق والمربعات والمكعبات، وحُل 30 مسألة.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="20" t="inlineStr">
+      <c r="A3" s="27" t="inlineStr">
         <is>
           <t>اليوم 2</t>
         </is>
       </c>
-      <c r="B3" s="21" t="inlineStr">
+      <c r="B3" s="28" t="inlineStr">
         <is>
           <t>متتاليات الحروف + الشكل المكمل</t>
         </is>
       </c>
-      <c r="C3" s="21" t="inlineStr">
+      <c r="C3" s="28" t="inlineStr">
         <is>
           <t>اكتب ترتيب الحروف على ورقة، وحل السلسلتين بخطوتين.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="20" t="inlineStr">
+      <c r="A4" s="27" t="inlineStr">
         <is>
           <t>اليوم 3</t>
         </is>
       </c>
-      <c r="B4" s="21" t="inlineStr">
+      <c r="B4" s="28" t="inlineStr">
         <is>
           <t>المكعبات</t>
         </is>
       </c>
-      <c r="C4" s="21" t="inlineStr">
+      <c r="C4" s="28" t="inlineStr">
         <is>
           <t>الاستبعاد - المثلثات - عقارب الساعة (بمكعب ورقي حقيقي).</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="20" t="inlineStr">
+      <c r="A5" s="27" t="inlineStr">
         <is>
           <t>اليوم 4</t>
         </is>
       </c>
-      <c r="B5" s="21" t="inlineStr">
+      <c r="B5" s="28" t="inlineStr">
         <is>
           <t>التصور المكاني + التدوير (بيردو)</t>
         </is>
       </c>
-      <c r="C5" s="21" t="inlineStr">
+      <c r="C5" s="28" t="inlineStr">
         <is>
           <t>استخدم علبة ثقاب أو مكعبًا ودوّره بيدك.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="20" t="inlineStr">
+      <c r="A6" s="27" t="inlineStr">
         <is>
           <t>اليوم 5</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr">
+      <c r="B6" s="28" t="inlineStr">
         <is>
           <t>الأشكال المتطابقة + تركيب X/Y/Z</t>
         </is>
       </c>
-      <c r="C6" s="21" t="inlineStr">
+      <c r="C6" s="28" t="inlineStr">
         <is>
           <t>ركز على الفرق بين التدوير والانعكاس.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="20" t="inlineStr">
+      <c r="A7" s="27" t="inlineStr">
         <is>
           <t>اليوم 6</t>
         </is>
       </c>
-      <c r="B7" s="21" t="inlineStr">
+      <c r="B7" s="28" t="inlineStr">
         <is>
           <t>المرايا وثني الورق + تعبيرات الوجه</t>
         </is>
       </c>
-      <c r="C7" s="21" t="inlineStr">
+      <c r="C7" s="28" t="inlineStr">
         <is>
           <t>جرب ثني الورق بيدك، واحفظ علامات المشاعر السبعة.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="20" t="inlineStr">
+      <c r="A8" s="27" t="inlineStr">
         <is>
           <t>اليوم 7</t>
         </is>
       </c>
-      <c r="B8" s="21" t="inlineStr">
+      <c r="B8" s="28" t="inlineStr">
         <is>
           <t>مراجعة شاملة + اختبار زمني</t>
         </is>
       </c>
-      <c r="C8" s="21" t="inlineStr">
+      <c r="C8" s="28" t="inlineStr">
         <is>
           <t>30 سؤالًا في 25 دقيقة.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="22" t="inlineStr">
+      <c r="A10" s="29" t="inlineStr">
         <is>
           <t>نصائح يوم الامتحان</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="23" t="inlineStr">
+      <c r="A11" s="30" t="inlineStr">
         <is>
           <t>• اقرأ رأس السؤال: هل المطلوب الصحيح أم «الخاطئ» أم «المختلف»؟</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="23" t="inlineStr">
+      <c r="A12" s="30" t="inlineStr">
         <is>
           <t>• لا تتوقف أكثر من 45 ثانية على السؤال — علّمه وارجع إليه.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="23" t="inlineStr">
+      <c r="A13" s="30" t="inlineStr">
         <is>
           <t>• استخدم الاستبعاد قبل التخيّل: حذف اختيارين يرفع إصابتك من 25% إلى 50%.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="23" t="inlineStr">
+      <c r="A14" s="30" t="inlineStr">
         <is>
           <t>• في الأشكال: سمِّ الأشكال بصوت منخفض (مثلث، دائرة، مربع).</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="23" t="inlineStr">
+      <c r="A15" s="30" t="inlineStr">
         <is>
           <t>• اكتب الفروق بين الأرقام فوق السلسلة مباشرة.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="23" t="inlineStr">
+      <c r="A16" s="30" t="inlineStr">
         <is>
           <t>• راجع في آخر 5 دقائق: تأكد أنك لم تختر «الصحيح» في سؤال يطلب «الخاطئ».</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="23" t="inlineStr">
+      <c r="A17" s="30" t="inlineStr">
         <is>
           <t>• التدريب أهم من الحفظ: نفس الأسئلة تتكرر بأشكال قريبة جدًا.</t>
         </is>
